--- a/src/aw-dawid/poland_ab.xlsx
+++ b/src/aw-dawid/poland_ab.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d\Documents\GitHub\poland-ab-mda\src\aw-dawid\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E646EEFC-7596-4D13-A868-783D8160E383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C52895-09C2-433C-9090-D4C5FF008C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E84E2F30-E922-4112-8AE8-9E12D9A82DDF}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="raw_data" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DESCRIPTION!$A$1:$D$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DESCRIPTION!$A$1:$D$57</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="144">
   <si>
     <t>grupa</t>
   </si>
@@ -138,9 +138,6 @@
     <t>x10</t>
   </si>
   <si>
-    <t>studencki uczelni na 10,000 ludnosci - 2024</t>
-  </si>
-  <si>
     <t>x45</t>
   </si>
   <si>
@@ -156,21 +153,12 @@
     <t>x13</t>
   </si>
   <si>
-    <t>pkb na osobę w 2023 w zl</t>
-  </si>
-  <si>
     <t>x14</t>
   </si>
   <si>
-    <t>podmioty wpisane do rejestru REGON na 10 tys. Ludności – 2024</t>
-  </si>
-  <si>
     <t>x15</t>
   </si>
   <si>
-    <t>dochody budżetów województw na 1 mieszkanca w roku 2024.</t>
-  </si>
-  <si>
     <t>x16</t>
   </si>
   <si>
@@ -180,9 +168,6 @@
     <t>x17</t>
   </si>
   <si>
-    <t>Przeciętne miesięczne wynagrodzenia brutto w 2024</t>
-  </si>
-  <si>
     <t>INSRASTRUKTURA TRANSPORTOWA</t>
   </si>
   <si>
@@ -192,54 +177,36 @@
     <t>x18</t>
   </si>
   <si>
-    <t>liczba rowerow publicznych na 1000 ludnosciu 2024</t>
-  </si>
-  <si>
     <t>x47</t>
   </si>
   <si>
     <t>x19</t>
   </si>
   <si>
-    <t>drogi dla rowerow na 10,000 km2 2024</t>
-  </si>
-  <si>
     <t>x48</t>
   </si>
   <si>
     <t>x20</t>
   </si>
   <si>
-    <t>kilometry drog publiczncyh ogolem - liczba bezwgledna - 2024</t>
-  </si>
-  <si>
     <t>x49</t>
   </si>
   <si>
     <t>x21</t>
   </si>
   <si>
-    <t>kilometry drog publiczncyh o nawierzchni twardej - liczba bezwgledna - 2024</t>
-  </si>
-  <si>
     <t>x50</t>
   </si>
   <si>
     <t>x22</t>
   </si>
   <si>
-    <t>ogółem (przystanki autobusowe (z trolejbusowymi) i tramwajowe, przystanki wspólne dla tramwajów i autobusów) 2024</t>
-  </si>
-  <si>
     <t>x51</t>
   </si>
   <si>
     <t>x23</t>
   </si>
   <si>
-    <t>długość linii komunikacji miejskiej na 1000 mieszkańców 2024</t>
-  </si>
-  <si>
     <t>x52</t>
   </si>
   <si>
@@ -255,84 +222,45 @@
     <t>x25</t>
   </si>
   <si>
-    <t>LINIE REGULARNEJ KOMUNIKACJI AUTOBUSOWEJ  w km w 2024</t>
-  </si>
-  <si>
     <t>x54</t>
   </si>
   <si>
     <t>x26</t>
   </si>
   <si>
-    <t>linie kolejowe ogółem na 100 km2 w 2024</t>
-  </si>
-  <si>
     <t>x55</t>
   </si>
   <si>
     <t>x27</t>
   </si>
   <si>
-    <t>samochody osobowe na 1000 mieszkancow 2024</t>
-  </si>
-  <si>
     <t>x56</t>
   </si>
   <si>
     <t>INWESTYCJE</t>
   </si>
   <si>
-    <t>nakłady inwestycyjne w przedsiębiorstwach na 1 mieszkańca w 2024</t>
-  </si>
-  <si>
     <t>x11</t>
   </si>
   <si>
-    <t xml:space="preserve"> WYDATKI BUDŻETÓW GMIN I MIAST NA PRAWACH POWIATU na 1 mieszkanca w 2024</t>
-  </si>
-  <si>
-    <t>Wydatki budzetów gmin I miast na prawach powiatu na kulturę I ochronę dziedzictwa narodowego na 1 mieszkanca w 2024</t>
-  </si>
-  <si>
     <t>x32</t>
   </si>
   <si>
-    <t>Wydatki budzetów gmin I miast na prawach powiatu na oświatena 1 mieszkanca w 2024</t>
-  </si>
-  <si>
     <t>x33</t>
   </si>
   <si>
     <t>wydatki budzetów gmin I miast na prawach powiatu na Ochrona powietrza atmosferycznego i klimatu na 1 mieszkanca w 2024</t>
   </si>
   <si>
-    <t>wydatki inwestycyjne budzetów gmin I miast na prawach powiatu na 1 mieszkanca w 2024</t>
-  </si>
-  <si>
     <t>KULTURA</t>
   </si>
   <si>
-    <t>biblioteki publiczne na 10 000 ludności w 2024</t>
-  </si>
-  <si>
     <t>x36</t>
   </si>
   <si>
-    <t>pozycje księgozbioru bibliotek publicznych na 1 000 ludności</t>
-  </si>
-  <si>
     <t>x37</t>
   </si>
   <si>
-    <t>średnia liczba godzin otwarcia biblioteki publicznej po godz. 16.00 w 2024</t>
-  </si>
-  <si>
-    <t>zajęcia prowadzone przez teatry i instytucje muzyczne, muzea oraz centra, domy, ośrodki kultury, kluby i świetlice na 1000 ludności w 2024</t>
-  </si>
-  <si>
-    <t>uczestnicy imprez (wydarzeń kulturalnych) organizowanych przez teatry i instytucje muzyczne, muzea, galerie sztuki, kina oraz centra, ośrodki kultury, domy kultury, kluby i świetlice na 1 000 ludności w 2024</t>
-  </si>
-  <si>
     <t>OCHRONA ZDROWIA</t>
   </si>
   <si>
@@ -357,36 +285,18 @@
     <t>x44</t>
   </si>
   <si>
-    <t>łóżka na oddziałach kardiologicznych na 10 tys. ludności</t>
-  </si>
-  <si>
     <t>STAN MATERIALNY</t>
   </si>
   <si>
-    <t>Stopa % bezrobocia w grudniu 2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BENEFICJENCI ŚRODOWISKOWEJ POMOCY SPOŁECZNEJ w %</t>
-  </si>
-  <si>
     <t>TURYSTYKA</t>
   </si>
   <si>
     <t>miejsca noclegowe na 1000 ludnosci w 2024</t>
   </si>
   <si>
-    <t>udzielone noclegi ogółem styczeń-grudzień na 10000 ludności w 2024</t>
-  </si>
-  <si>
     <t>WARUNKI BYTOWE</t>
   </si>
   <si>
-    <t>Liczba mieszkań na 1000 mieszkańców w 2024 r</t>
-  </si>
-  <si>
-    <t>Odsetek ludności w obiektach  zbiorowego zakwaterowania 2021</t>
-  </si>
-  <si>
     <t>liczba miejsc w domach studenckich w stosunku do liczby studentow 2024 - jaki odsetek studentow domy domy studenckie są w stanie pomieścić</t>
   </si>
   <si>
@@ -396,9 +306,6 @@
     <t>x57</t>
   </si>
   <si>
-    <t>zasoby mieszkaniowe gim komunalne 2024</t>
-  </si>
-  <si>
     <t>ZASOBY LUDZKIE</t>
   </si>
   <si>
@@ -471,17 +378,107 @@
     <t>saldo migracji stałej w % rok do roku - 2024</t>
   </si>
   <si>
-    <t>wypadki drogowe na 10,000 mieszkancow 2024</t>
-  </si>
-  <si>
-    <t>populacja - szacunki gusu 1 stycznia 2025</t>
+    <t>studencki uczelni na 1,000 ludnosci - 2024</t>
+  </si>
+  <si>
+    <t>pkb na osobę w 2023 w 1000 zl</t>
+  </si>
+  <si>
+    <t>podmioty wpisane do rejestru REGON na 1 tys. Ludności – 2024</t>
+  </si>
+  <si>
+    <t>dochody budżetów województw na 1 mieszkanca w roku 2024 w dziesiątkach złotych]</t>
+  </si>
+  <si>
+    <t>Przeciętne miesięczne wynagrodzenia brutto w 2024 w setkach zł</t>
+  </si>
+  <si>
+    <t>liczba rowerow publicznych na 100,000 ludnosciu 2024</t>
+  </si>
+  <si>
+    <t>drogi dla rowerow na 1,000 km2 2024</t>
+  </si>
+  <si>
+    <t>kilometry drog publiczncyh ogolem na 100 km^2 - 2024</t>
+  </si>
+  <si>
+    <t>kilometry drog publiczncyh o nawierzchni twardej na 100 km^2 - 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (przystanki autobusowe (z trolejbusowymi) i tramwajowe, przystanki wspólne dla tramwajów i autobusów) na 100km^2 w  2024</t>
+  </si>
+  <si>
+    <t>długość linii komunikacji miejskiej na 100,000 mieszkańców 2024 w km</t>
+  </si>
+  <si>
+    <t>LINIE REGULARNEJ KOMUNIKACJI AUTOBUSOWEJ  w km na 100km^2 w 2024</t>
+  </si>
+  <si>
+    <t>linie kolejowe ogółem na 1000 km2 w 2024</t>
+  </si>
+  <si>
+    <t>samochody osobowe na 100 mieszkancow 2024</t>
+  </si>
+  <si>
+    <t>wypadki drogowe na 100,000 mieszkancow 2024</t>
+  </si>
+  <si>
+    <t>nakłady inwestycyjne w przedsiębiorstwach na 1 mieszkańca w 2024 w setkach zł</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> WYDATKI BUDŻETÓW GMIN I MIAST NA PRAWACH POWIATU na 1 mieszkanca w 2024 w setkach zł</t>
+  </si>
+  <si>
+    <t>Wydatki budzetów gmin I miast na prawach powiatu na kulturę I ochronę dziedzictwa narodowego na 1 mieszkanca w 2024 w dziesiątkach złotych</t>
+  </si>
+  <si>
+    <t>Wydatki budzetów gmin I miast na prawach powiatu na oświatena 1 mieszkanca w 2024 w setkach zł</t>
+  </si>
+  <si>
+    <t>wydatki inwestycyjne budzetów gmin I miast na prawach powiatu na 1 mieszkanca w 2024 w setkach zł</t>
+  </si>
+  <si>
+    <t>pozycje księgozbioru bibliotek publicznych na 100 ludności</t>
+  </si>
+  <si>
+    <t>biblioteki publiczne na 100,000 ludności w 2024</t>
+  </si>
+  <si>
+    <t>średnia liczba godzin otwarcia biblioteki publicznej po godz. 16.00 w 2024 / powiększone 10-krotnie</t>
+  </si>
+  <si>
+    <t>zajęcia prowadzone przez teatry i instytucje muzyczne, muzea oraz centra, domy, ośrodki kultury, kluby i świetlice na 10,000 ludności w 2024</t>
+  </si>
+  <si>
+    <t>uczestnicy imprez (wydarzeń kulturalnych) organizowanych przez teatry i instytucje muzyczne, muzea, galerie sztuki, kina oraz centra, ośrodki kultury, domy kultury, kluby i świetlice na 1,000 ludności w 2024</t>
+  </si>
+  <si>
+    <t>łóżka na oddziałach kardiologicznych na 100 tys. ludności</t>
+  </si>
+  <si>
+    <t>Stopa promil bezrobocia w grudniu 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BENEFICJENCI ŚRODOWISKOWEJ POMOCY SPOŁECZNEJ w promilach</t>
+  </si>
+  <si>
+    <t>udzielone noclegi ogółem styczeń-grudzień na 10 ludności w 2024</t>
+  </si>
+  <si>
+    <t>Liczba mieszkań na 100 mieszkańców w 2024 r</t>
+  </si>
+  <si>
+    <t>Odsetek ludności w obiektach  zbiorowego zakwaterowania 2021 / powiększone 100-krotnie</t>
+  </si>
+  <si>
+    <t>zasoby mieszkaniowe gim komunalne 2024 na 10,000 mieszkancow</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -539,7 +536,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -618,6 +615,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -632,7 +641,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -651,59 +660,20 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -8230,7 +8200,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52CBCD04-BED9-43FB-A9EC-F2FDF9191772}">
   <dimension ref="A1:Z88"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -8238,7 +8208,7 @@
     <col min="4" max="4" width="165.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8252,1113 +8222,1107 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>144</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>142</v>
+      <c r="D8" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>113</v>
+      </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>115</v>
+      </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="3" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D18" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="B19" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>119</v>
+      </c>
     </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>44</v>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>46</v>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>121</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" s="16" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>50</v>
       </c>
+      <c r="D22" s="4" t="s">
+        <v>122</v>
+      </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="4" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>53</v>
+      <c r="D23" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="4" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" s="16" t="s">
+      <c r="D24" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>56</v>
       </c>
+      <c r="D25" s="4" t="s">
+        <v>124</v>
+      </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="16" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>59</v>
       </c>
+      <c r="D26" s="17" t="s">
+        <v>125</v>
+      </c>
     </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="4" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>62</v>
+      <c r="D27" s="15" t="s">
+        <v>126</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="4" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="D28" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
         <v>65</v>
       </c>
+      <c r="B29" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>128</v>
+      </c>
     </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>85</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>87</v>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" s="5" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>88</v>
+      <c r="D35" s="6" t="s">
+        <v>132</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>90</v>
+        <v>134</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="B37" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>92</v>
+      <c r="C38" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>94</v>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>95</v>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="B42" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B54" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C42" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>100</v>
+      <c r="C54" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>102</v>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>103</v>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>105</v>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B46" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>107</v>
-      </c>
+    <row r="73" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H73" s="18"/>
+      <c r="I73" s="18"/>
+      <c r="J73" s="18"/>
+      <c r="K73" s="18"/>
+      <c r="L73" s="18"/>
+      <c r="M73" s="18"/>
+      <c r="N73" s="18"/>
+      <c r="O73" s="18"/>
+      <c r="P73" s="18"/>
+      <c r="Q73" s="18"/>
+      <c r="R73" s="18"/>
+      <c r="S73" s="18"/>
+      <c r="T73" s="18"/>
+      <c r="U73" s="18"/>
+      <c r="V73" s="18"/>
+      <c r="W73" s="18"/>
     </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>108</v>
-      </c>
+    <row r="74" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H74" s="19"/>
+      <c r="I74" s="18"/>
+      <c r="J74" s="18"/>
+      <c r="K74" s="18"/>
+      <c r="L74" s="18"/>
+      <c r="M74" s="18"/>
+      <c r="N74" s="18"/>
+      <c r="O74" s="18"/>
+      <c r="P74" s="18"/>
+      <c r="Q74" s="18"/>
+      <c r="R74" s="18"/>
+      <c r="S74" s="18"/>
+      <c r="T74" s="18"/>
+      <c r="U74" s="18"/>
+      <c r="V74" s="18"/>
+      <c r="W74" s="18"/>
+      <c r="X74" s="18"/>
+      <c r="Z74" s="18"/>
     </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>110</v>
-      </c>
+    <row r="75" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H75" s="19"/>
+      <c r="I75" s="18"/>
+      <c r="J75" s="18"/>
+      <c r="K75" s="18"/>
+      <c r="L75" s="18"/>
+      <c r="M75" s="18"/>
+      <c r="N75" s="18"/>
+      <c r="O75" s="18"/>
+      <c r="P75" s="18"/>
+      <c r="Q75" s="18"/>
+      <c r="R75" s="18"/>
+      <c r="S75" s="18"/>
+      <c r="T75" s="18"/>
+      <c r="U75" s="18"/>
+      <c r="V75" s="18"/>
+      <c r="W75" s="18"/>
+      <c r="X75" s="18"/>
+      <c r="Z75" s="18"/>
     </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>111</v>
-      </c>
+    <row r="76" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H76" s="19"/>
+      <c r="I76" s="18"/>
+      <c r="J76" s="18"/>
+      <c r="K76" s="18"/>
+      <c r="L76" s="18"/>
+      <c r="M76" s="18"/>
+      <c r="N76" s="18"/>
+      <c r="O76" s="18"/>
+      <c r="P76" s="18"/>
+      <c r="Q76" s="18"/>
+      <c r="R76" s="18"/>
+      <c r="S76" s="18"/>
+      <c r="T76" s="18"/>
+      <c r="U76" s="18"/>
+      <c r="V76" s="18"/>
+      <c r="W76" s="18"/>
+      <c r="X76" s="18"/>
+      <c r="Z76" s="18"/>
     </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>113</v>
-      </c>
+    <row r="77" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H77" s="19"/>
+      <c r="I77" s="18"/>
+      <c r="J77" s="18"/>
+      <c r="K77" s="18"/>
+      <c r="L77" s="18"/>
+      <c r="M77" s="18"/>
+      <c r="N77" s="18"/>
+      <c r="O77" s="18"/>
+      <c r="P77" s="18"/>
+      <c r="Q77" s="18"/>
+      <c r="R77" s="18"/>
+      <c r="S77" s="18"/>
+      <c r="T77" s="18"/>
+      <c r="U77" s="18"/>
+      <c r="V77" s="18"/>
+      <c r="W77" s="18"/>
+      <c r="X77" s="18"/>
+      <c r="Z77" s="18"/>
     </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>114</v>
-      </c>
+    <row r="78" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H78" s="19"/>
+      <c r="I78" s="18"/>
+      <c r="J78" s="18"/>
+      <c r="K78" s="18"/>
+      <c r="L78" s="18"/>
+      <c r="M78" s="18"/>
+      <c r="N78" s="18"/>
+      <c r="O78" s="18"/>
+      <c r="P78" s="18"/>
+      <c r="Q78" s="18"/>
+      <c r="R78" s="18"/>
+      <c r="S78" s="18"/>
+      <c r="T78" s="18"/>
+      <c r="U78" s="18"/>
+      <c r="V78" s="18"/>
+      <c r="W78" s="18"/>
+      <c r="X78" s="18"/>
+      <c r="Z78" s="18"/>
     </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>115</v>
-      </c>
+    <row r="79" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H79" s="19"/>
+      <c r="I79" s="18"/>
+      <c r="J79" s="18"/>
+      <c r="K79" s="18"/>
+      <c r="L79" s="18"/>
+      <c r="M79" s="18"/>
+      <c r="N79" s="18"/>
+      <c r="O79" s="18"/>
+      <c r="P79" s="18"/>
+      <c r="Q79" s="18"/>
+      <c r="R79" s="18"/>
+      <c r="S79" s="18"/>
+      <c r="T79" s="18"/>
+      <c r="U79" s="18"/>
+      <c r="V79" s="18"/>
+      <c r="W79" s="18"/>
+      <c r="X79" s="18"/>
+      <c r="Z79" s="18"/>
     </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>116</v>
-      </c>
+    <row r="80" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H80" s="19"/>
+      <c r="I80" s="18"/>
+      <c r="J80" s="18"/>
+      <c r="K80" s="18"/>
+      <c r="L80" s="18"/>
+      <c r="M80" s="18"/>
+      <c r="N80" s="18"/>
+      <c r="O80" s="18"/>
+      <c r="P80" s="18"/>
+      <c r="Q80" s="18"/>
+      <c r="R80" s="18"/>
+      <c r="S80" s="18"/>
+      <c r="T80" s="18"/>
+      <c r="U80" s="18"/>
+      <c r="V80" s="18"/>
+      <c r="W80" s="18"/>
+      <c r="X80" s="18"/>
+      <c r="Z80" s="18"/>
     </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>118</v>
-      </c>
+    <row r="81" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H81" s="19"/>
+      <c r="I81" s="18"/>
+      <c r="J81" s="18"/>
+      <c r="K81" s="18"/>
+      <c r="L81" s="18"/>
+      <c r="M81" s="18"/>
+      <c r="N81" s="18"/>
+      <c r="O81" s="18"/>
+      <c r="P81" s="18"/>
+      <c r="Q81" s="18"/>
+      <c r="R81" s="18"/>
+      <c r="S81" s="18"/>
+      <c r="T81" s="18"/>
+      <c r="U81" s="18"/>
+      <c r="V81" s="18"/>
+      <c r="W81" s="18"/>
+      <c r="X81" s="18"/>
+      <c r="Z81" s="18"/>
     </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B55" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>120</v>
-      </c>
+    <row r="82" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H82" s="19"/>
+      <c r="I82" s="18"/>
+      <c r="J82" s="18"/>
+      <c r="K82" s="18"/>
+      <c r="L82" s="18"/>
+      <c r="M82" s="18"/>
+      <c r="N82" s="18"/>
+      <c r="O82" s="18"/>
+      <c r="P82" s="18"/>
+      <c r="Q82" s="18"/>
+      <c r="R82" s="18"/>
+      <c r="S82" s="18"/>
+      <c r="T82" s="18"/>
+      <c r="U82" s="18"/>
+      <c r="V82" s="18"/>
+      <c r="W82" s="18"/>
+      <c r="X82" s="18"/>
+      <c r="Z82" s="18"/>
     </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D56" s="10" t="s">
-        <v>121</v>
-      </c>
+    <row r="83" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H83" s="19"/>
+      <c r="I83" s="18"/>
+      <c r="J83" s="18"/>
+      <c r="K83" s="18"/>
+      <c r="L83" s="18"/>
+      <c r="M83" s="18"/>
+      <c r="N83" s="18"/>
+      <c r="O83" s="18"/>
+      <c r="P83" s="18"/>
+      <c r="Q83" s="18"/>
+      <c r="R83" s="18"/>
+      <c r="S83" s="18"/>
+      <c r="T83" s="18"/>
+      <c r="U83" s="18"/>
+      <c r="V83" s="18"/>
+      <c r="W83" s="18"/>
+      <c r="X83" s="18"/>
+      <c r="Z83" s="18"/>
     </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D57" s="10" t="s">
-        <v>122</v>
-      </c>
+    <row r="84" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H84" s="19"/>
+      <c r="I84" s="18"/>
+      <c r="J84" s="18"/>
+      <c r="K84" s="18"/>
+      <c r="L84" s="18"/>
+      <c r="M84" s="18"/>
+      <c r="N84" s="18"/>
+      <c r="O84" s="18"/>
+      <c r="P84" s="18"/>
+      <c r="Q84" s="18"/>
+      <c r="R84" s="18"/>
+      <c r="S84" s="18"/>
+      <c r="T84" s="18"/>
+      <c r="U84" s="18"/>
+      <c r="V84" s="18"/>
+      <c r="W84" s="18"/>
+      <c r="X84" s="18"/>
+      <c r="Z84" s="18"/>
     </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>123</v>
-      </c>
+    <row r="85" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H85" s="19"/>
+      <c r="I85" s="18"/>
+      <c r="J85" s="18"/>
+      <c r="K85" s="18"/>
+      <c r="L85" s="18"/>
+      <c r="M85" s="18"/>
+      <c r="N85" s="18"/>
+      <c r="O85" s="18"/>
+      <c r="P85" s="18"/>
+      <c r="Q85" s="18"/>
+      <c r="R85" s="18"/>
+      <c r="S85" s="18"/>
+      <c r="T85" s="18"/>
+      <c r="U85" s="18"/>
+      <c r="V85" s="18"/>
+      <c r="W85" s="18"/>
+      <c r="X85" s="18"/>
+      <c r="Z85" s="18"/>
     </row>
-    <row r="73" spans="8:26">
-      <c r="H73" s="19"/>
-      <c r="I73" s="19"/>
-      <c r="J73" s="19"/>
-      <c r="K73" s="19"/>
-      <c r="L73" s="19"/>
-      <c r="M73" s="19"/>
-      <c r="N73" s="19"/>
-      <c r="O73" s="19"/>
-      <c r="P73" s="19"/>
-      <c r="Q73" s="19"/>
-      <c r="R73" s="19"/>
-      <c r="S73" s="19"/>
-      <c r="T73" s="19"/>
-      <c r="U73" s="19"/>
-      <c r="V73" s="19"/>
-      <c r="W73" s="19"/>
+    <row r="86" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H86" s="19"/>
+      <c r="I86" s="18"/>
+      <c r="J86" s="18"/>
+      <c r="K86" s="18"/>
+      <c r="L86" s="18"/>
+      <c r="M86" s="18"/>
+      <c r="N86" s="18"/>
+      <c r="O86" s="18"/>
+      <c r="P86" s="18"/>
+      <c r="Q86" s="18"/>
+      <c r="R86" s="18"/>
+      <c r="S86" s="18"/>
+      <c r="T86" s="18"/>
+      <c r="U86" s="18"/>
+      <c r="V86" s="18"/>
+      <c r="W86" s="18"/>
+      <c r="X86" s="18"/>
+      <c r="Z86" s="18"/>
     </row>
-    <row r="74" spans="8:26">
-      <c r="H74" s="20"/>
-      <c r="I74" s="19"/>
-      <c r="J74" s="19"/>
-      <c r="K74" s="19"/>
-      <c r="L74" s="19"/>
-      <c r="M74" s="19"/>
-      <c r="N74" s="19"/>
-      <c r="O74" s="19"/>
-      <c r="P74" s="19"/>
-      <c r="Q74" s="19"/>
-      <c r="R74" s="19"/>
-      <c r="S74" s="19"/>
-      <c r="T74" s="19"/>
-      <c r="U74" s="19"/>
-      <c r="V74" s="19"/>
-      <c r="W74" s="19"/>
-      <c r="X74" s="19"/>
-      <c r="Z74" s="19"/>
+    <row r="87" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H87" s="19"/>
+      <c r="I87" s="18"/>
+      <c r="J87" s="18"/>
+      <c r="K87" s="18"/>
+      <c r="L87" s="18"/>
+      <c r="M87" s="18"/>
+      <c r="N87" s="18"/>
+      <c r="O87" s="18"/>
+      <c r="P87" s="18"/>
+      <c r="Q87" s="18"/>
+      <c r="R87" s="18"/>
+      <c r="S87" s="18"/>
+      <c r="T87" s="18"/>
+      <c r="U87" s="18"/>
+      <c r="V87" s="18"/>
+      <c r="W87" s="18"/>
+      <c r="X87" s="18"/>
+      <c r="Z87" s="18"/>
     </row>
-    <row r="75" spans="8:26">
-      <c r="H75" s="20"/>
-      <c r="I75" s="19"/>
-      <c r="J75" s="19"/>
-      <c r="K75" s="19"/>
-      <c r="L75" s="19"/>
-      <c r="M75" s="19"/>
-      <c r="N75" s="19"/>
-      <c r="O75" s="19"/>
-      <c r="P75" s="19"/>
-      <c r="Q75" s="19"/>
-      <c r="R75" s="19"/>
-      <c r="S75" s="19"/>
-      <c r="T75" s="19"/>
-      <c r="U75" s="19"/>
-      <c r="V75" s="19"/>
-      <c r="W75" s="19"/>
-      <c r="X75" s="19"/>
-      <c r="Z75" s="19"/>
-    </row>
-    <row r="76" spans="8:26">
-      <c r="H76" s="20"/>
-      <c r="I76" s="19"/>
-      <c r="J76" s="19"/>
-      <c r="K76" s="19"/>
-      <c r="L76" s="19"/>
-      <c r="M76" s="19"/>
-      <c r="N76" s="19"/>
-      <c r="O76" s="19"/>
-      <c r="P76" s="19"/>
-      <c r="Q76" s="19"/>
-      <c r="R76" s="19"/>
-      <c r="S76" s="19"/>
-      <c r="T76" s="19"/>
-      <c r="U76" s="19"/>
-      <c r="V76" s="19"/>
-      <c r="W76" s="19"/>
-      <c r="X76" s="19"/>
-      <c r="Z76" s="19"/>
-    </row>
-    <row r="77" spans="8:26">
-      <c r="H77" s="20"/>
-      <c r="I77" s="19"/>
-      <c r="J77" s="19"/>
-      <c r="K77" s="19"/>
-      <c r="L77" s="19"/>
-      <c r="M77" s="19"/>
-      <c r="N77" s="19"/>
-      <c r="O77" s="19"/>
-      <c r="P77" s="19"/>
-      <c r="Q77" s="19"/>
-      <c r="R77" s="19"/>
-      <c r="S77" s="19"/>
-      <c r="T77" s="19"/>
-      <c r="U77" s="19"/>
-      <c r="V77" s="19"/>
-      <c r="W77" s="19"/>
-      <c r="X77" s="19"/>
-      <c r="Z77" s="19"/>
-    </row>
-    <row r="78" spans="8:26">
-      <c r="H78" s="20"/>
-      <c r="I78" s="19"/>
-      <c r="J78" s="19"/>
-      <c r="K78" s="19"/>
-      <c r="L78" s="19"/>
-      <c r="M78" s="19"/>
-      <c r="N78" s="19"/>
-      <c r="O78" s="19"/>
-      <c r="P78" s="19"/>
-      <c r="Q78" s="19"/>
-      <c r="R78" s="19"/>
-      <c r="S78" s="19"/>
-      <c r="T78" s="19"/>
-      <c r="U78" s="19"/>
-      <c r="V78" s="19"/>
-      <c r="W78" s="19"/>
-      <c r="X78" s="19"/>
-      <c r="Z78" s="19"/>
-    </row>
-    <row r="79" spans="8:26">
-      <c r="H79" s="20"/>
-      <c r="I79" s="19"/>
-      <c r="J79" s="19"/>
-      <c r="K79" s="19"/>
-      <c r="L79" s="19"/>
-      <c r="M79" s="19"/>
-      <c r="N79" s="19"/>
-      <c r="O79" s="19"/>
-      <c r="P79" s="19"/>
-      <c r="Q79" s="19"/>
-      <c r="R79" s="19"/>
-      <c r="S79" s="19"/>
-      <c r="T79" s="19"/>
-      <c r="U79" s="19"/>
-      <c r="V79" s="19"/>
-      <c r="W79" s="19"/>
-      <c r="X79" s="19"/>
-      <c r="Z79" s="19"/>
-    </row>
-    <row r="80" spans="8:26">
-      <c r="H80" s="20"/>
-      <c r="I80" s="19"/>
-      <c r="J80" s="19"/>
-      <c r="K80" s="19"/>
-      <c r="L80" s="19"/>
-      <c r="M80" s="19"/>
-      <c r="N80" s="19"/>
-      <c r="O80" s="19"/>
-      <c r="P80" s="19"/>
-      <c r="Q80" s="19"/>
-      <c r="R80" s="19"/>
-      <c r="S80" s="19"/>
-      <c r="T80" s="19"/>
-      <c r="U80" s="19"/>
-      <c r="V80" s="19"/>
-      <c r="W80" s="19"/>
-      <c r="X80" s="19"/>
-      <c r="Z80" s="19"/>
-    </row>
-    <row r="81" spans="8:26">
-      <c r="H81" s="20"/>
-      <c r="I81" s="19"/>
-      <c r="J81" s="19"/>
-      <c r="K81" s="19"/>
-      <c r="L81" s="19"/>
-      <c r="M81" s="19"/>
-      <c r="N81" s="19"/>
-      <c r="O81" s="19"/>
-      <c r="P81" s="19"/>
-      <c r="Q81" s="19"/>
-      <c r="R81" s="19"/>
-      <c r="S81" s="19"/>
-      <c r="T81" s="19"/>
-      <c r="U81" s="19"/>
-      <c r="V81" s="19"/>
-      <c r="W81" s="19"/>
-      <c r="X81" s="19"/>
-      <c r="Z81" s="19"/>
-    </row>
-    <row r="82" spans="8:26">
-      <c r="H82" s="20"/>
-      <c r="I82" s="19"/>
-      <c r="J82" s="19"/>
-      <c r="K82" s="19"/>
-      <c r="L82" s="19"/>
-      <c r="M82" s="19"/>
-      <c r="N82" s="19"/>
-      <c r="O82" s="19"/>
-      <c r="P82" s="19"/>
-      <c r="Q82" s="19"/>
-      <c r="R82" s="19"/>
-      <c r="S82" s="19"/>
-      <c r="T82" s="19"/>
-      <c r="U82" s="19"/>
-      <c r="V82" s="19"/>
-      <c r="W82" s="19"/>
-      <c r="X82" s="19"/>
-      <c r="Z82" s="19"/>
-    </row>
-    <row r="83" spans="8:26">
-      <c r="H83" s="20"/>
-      <c r="I83" s="19"/>
-      <c r="J83" s="19"/>
-      <c r="K83" s="19"/>
-      <c r="L83" s="19"/>
-      <c r="M83" s="19"/>
-      <c r="N83" s="19"/>
-      <c r="O83" s="19"/>
-      <c r="P83" s="19"/>
-      <c r="Q83" s="19"/>
-      <c r="R83" s="19"/>
-      <c r="S83" s="19"/>
-      <c r="T83" s="19"/>
-      <c r="U83" s="19"/>
-      <c r="V83" s="19"/>
-      <c r="W83" s="19"/>
-      <c r="X83" s="19"/>
-      <c r="Z83" s="19"/>
-    </row>
-    <row r="84" spans="8:26">
-      <c r="H84" s="20"/>
-      <c r="I84" s="19"/>
-      <c r="J84" s="19"/>
-      <c r="K84" s="19"/>
-      <c r="L84" s="19"/>
-      <c r="M84" s="19"/>
-      <c r="N84" s="19"/>
-      <c r="O84" s="19"/>
-      <c r="P84" s="19"/>
-      <c r="Q84" s="19"/>
-      <c r="R84" s="19"/>
-      <c r="S84" s="19"/>
-      <c r="T84" s="19"/>
-      <c r="U84" s="19"/>
-      <c r="V84" s="19"/>
-      <c r="W84" s="19"/>
-      <c r="X84" s="19"/>
-      <c r="Z84" s="19"/>
-    </row>
-    <row r="85" spans="8:26">
-      <c r="H85" s="20"/>
-      <c r="I85" s="19"/>
-      <c r="J85" s="19"/>
-      <c r="K85" s="19"/>
-      <c r="L85" s="19"/>
-      <c r="M85" s="19"/>
-      <c r="N85" s="19"/>
-      <c r="O85" s="19"/>
-      <c r="P85" s="19"/>
-      <c r="Q85" s="19"/>
-      <c r="R85" s="19"/>
-      <c r="S85" s="19"/>
-      <c r="T85" s="19"/>
-      <c r="U85" s="19"/>
-      <c r="V85" s="19"/>
-      <c r="W85" s="19"/>
-      <c r="X85" s="19"/>
-      <c r="Z85" s="19"/>
-    </row>
-    <row r="86" spans="8:26">
-      <c r="H86" s="20"/>
-      <c r="I86" s="19"/>
-      <c r="J86" s="19"/>
-      <c r="K86" s="19"/>
-      <c r="L86" s="19"/>
-      <c r="M86" s="19"/>
-      <c r="N86" s="19"/>
-      <c r="O86" s="19"/>
-      <c r="P86" s="19"/>
-      <c r="Q86" s="19"/>
-      <c r="R86" s="19"/>
-      <c r="S86" s="19"/>
-      <c r="T86" s="19"/>
-      <c r="U86" s="19"/>
-      <c r="V86" s="19"/>
-      <c r="W86" s="19"/>
-      <c r="X86" s="19"/>
-      <c r="Z86" s="19"/>
-    </row>
-    <row r="87" spans="8:26">
-      <c r="H87" s="20"/>
-      <c r="I87" s="19"/>
-      <c r="J87" s="19"/>
-      <c r="K87" s="19"/>
-      <c r="L87" s="19"/>
-      <c r="M87" s="19"/>
-      <c r="N87" s="19"/>
-      <c r="O87" s="19"/>
-      <c r="P87" s="19"/>
-      <c r="Q87" s="19"/>
-      <c r="R87" s="19"/>
-      <c r="S87" s="19"/>
-      <c r="T87" s="19"/>
-      <c r="U87" s="19"/>
-      <c r="V87" s="19"/>
-      <c r="W87" s="19"/>
-      <c r="X87" s="19"/>
-      <c r="Z87" s="19"/>
-    </row>
-    <row r="88" spans="8:26">
-      <c r="H88" s="20"/>
-      <c r="I88" s="19"/>
-      <c r="J88" s="19"/>
-      <c r="K88" s="19"/>
-      <c r="L88" s="19"/>
-      <c r="M88" s="19"/>
-      <c r="N88" s="19"/>
-      <c r="O88" s="19"/>
-      <c r="P88" s="19"/>
-      <c r="Q88" s="19"/>
-      <c r="R88" s="19"/>
-      <c r="S88" s="19"/>
-      <c r="T88" s="19"/>
-      <c r="U88" s="19"/>
-      <c r="V88" s="19"/>
-      <c r="W88" s="19"/>
-      <c r="X88" s="19"/>
-      <c r="Z88" s="19"/>
+    <row r="88" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H88" s="19"/>
+      <c r="I88" s="18"/>
+      <c r="J88" s="18"/>
+      <c r="K88" s="18"/>
+      <c r="L88" s="18"/>
+      <c r="M88" s="18"/>
+      <c r="N88" s="18"/>
+      <c r="O88" s="18"/>
+      <c r="P88" s="18"/>
+      <c r="Q88" s="18"/>
+      <c r="R88" s="18"/>
+      <c r="S88" s="18"/>
+      <c r="T88" s="18"/>
+      <c r="U88" s="18"/>
+      <c r="V88" s="18"/>
+      <c r="W88" s="18"/>
+      <c r="X88" s="18"/>
+      <c r="Z88" s="18"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D58" xr:uid="{52CBCD04-BED9-43FB-A9EC-F2FDF9191772}">
@@ -9374,61 +9338,64 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3280568-C3F0-4084-9D93-93EB3596F459}">
-  <dimension ref="A1:BF39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:BE39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="8" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="9" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="7" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="7" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="45" width="5" bestFit="1" customWidth="1"/>
-    <col min="46" max="47" width="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="43" max="45" width="5" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="4" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="6" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="7" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="6" bestFit="1" customWidth="1"/>
     <col min="51" max="52" width="12" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="5" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="54" max="54" width="7" bestFit="1" customWidth="1"/>
     <col min="55" max="58" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s">
         <v>6</v>
@@ -9445,10 +9412,10 @@
       <c r="F1" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
       <c r="I1" t="s">
@@ -9461,55 +9428,55 @@
         <v>31</v>
       </c>
       <c r="L1" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="M1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" t="s">
         <v>37</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q1" t="s">
         <v>39</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>41</v>
       </c>
-      <c r="Q1" t="s">
-        <v>43</v>
-      </c>
-      <c r="R1" t="s">
-        <v>45</v>
-      </c>
       <c r="S1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="T1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U1" t="s">
+        <v>48</v>
+      </c>
+      <c r="V1" t="s">
+        <v>50</v>
+      </c>
+      <c r="W1" t="s">
         <v>52</v>
       </c>
-      <c r="U1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V1" t="s">
-        <v>58</v>
-      </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA1" t="s">
         <v>61</v>
       </c>
-      <c r="X1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>73</v>
-      </c>
       <c r="AB1" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="AC1" t="s">
         <v>24</v>
@@ -9524,10 +9491,10 @@
         <v>7</v>
       </c>
       <c r="AG1" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="AH1" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="AI1" t="s">
         <v>13</v>
@@ -9536,10 +9503,10 @@
         <v>16</v>
       </c>
       <c r="AK1" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="AL1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="AM1" t="s">
         <v>19</v>
@@ -9551,2994 +9518,2937 @@
         <v>27</v>
       </c>
       <c r="AP1" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AQ1" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AR1" t="s">
         <v>30</v>
       </c>
       <c r="AS1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="1">
+        <v>145</v>
+      </c>
+      <c r="C2" s="1">
+        <v>68</v>
+      </c>
+      <c r="D2" s="1">
+        <v>4.1988106967070049</v>
+      </c>
+      <c r="E2" s="1">
+        <v>12.7</v>
+      </c>
+      <c r="F2" s="1">
+        <v>99.504000000000005</v>
+      </c>
+      <c r="G2" s="1">
+        <v>100.14</v>
+      </c>
+      <c r="H2" s="2">
+        <v>964</v>
+      </c>
+      <c r="I2" s="2">
+        <v>14.412673879443586</v>
+      </c>
+      <c r="J2" s="2">
+        <v>43.6</v>
+      </c>
+      <c r="K2" s="2">
+        <v>82.6</v>
+      </c>
+      <c r="L2" s="3">
+        <v>96.997</v>
+      </c>
+      <c r="M2" s="3">
+        <v>158.9</v>
+      </c>
+      <c r="N2" s="3">
+        <v>59.802</v>
+      </c>
+      <c r="O2" s="3">
+        <v>112</v>
+      </c>
+      <c r="P2" s="3">
+        <v>88.674599999999998</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>94</v>
+      </c>
+      <c r="R2" s="4">
+        <v>72.710000000000008</v>
+      </c>
+      <c r="S2" s="4">
+        <v>123.49175314583647</v>
+      </c>
+      <c r="T2" s="4">
+        <v>105.12056950919938</v>
+      </c>
+      <c r="U2" s="4">
+        <v>63.357898430841729</v>
+      </c>
+      <c r="V2" s="4">
+        <v>170</v>
+      </c>
+      <c r="W2" s="4">
+        <v>78.12</v>
+      </c>
+      <c r="X2" s="4">
+        <v>137.16849651576678</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>62.167055480362897</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>65.398498439361902</v>
+      </c>
+      <c r="AB2" s="5">
+        <v>76.510000000000005</v>
+      </c>
+      <c r="AC2" s="5">
+        <v>95.189400000000006</v>
+      </c>
+      <c r="AD2" s="5">
+        <v>39.978999999999999</v>
+      </c>
+      <c r="AE2" s="5">
+        <v>31.475900000000003</v>
+      </c>
+      <c r="AF2" s="5">
+        <v>17.77</v>
+      </c>
+      <c r="AG2" s="5">
+        <v>16.377500000000001</v>
+      </c>
+      <c r="AH2" s="6">
+        <v>20</v>
+      </c>
+      <c r="AI2" s="6">
+        <v>28.333000000000002</v>
+      </c>
+      <c r="AJ2" s="6">
+        <v>45</v>
+      </c>
+      <c r="AK2" s="6">
+        <v>40</v>
+      </c>
+      <c r="AL2" s="6">
+        <v>166.5</v>
+      </c>
+      <c r="AM2" s="20">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="AN2" s="20">
+        <v>10.7</v>
+      </c>
+      <c r="AO2" s="20">
+        <v>55.7</v>
+      </c>
+      <c r="AP2" s="20">
+        <v>12.2</v>
+      </c>
+      <c r="AQ2" s="20">
+        <v>18.3</v>
+      </c>
+      <c r="AR2" s="11">
+        <v>46</v>
+      </c>
+      <c r="AS2" s="11">
+        <v>23</v>
+      </c>
+      <c r="AT2" s="8">
+        <v>29.87</v>
+      </c>
+      <c r="AU2" s="8">
+        <v>39.159999999999997</v>
+      </c>
+      <c r="AV2" s="21">
+        <v>46.3</v>
+      </c>
+      <c r="AW2" s="21">
+        <v>84.343869346007111</v>
+      </c>
+      <c r="AX2" s="21">
+        <v>6.848065303509264</v>
+      </c>
+      <c r="AY2" s="21">
+        <v>4.7</v>
+      </c>
+      <c r="AZ2" s="21">
+        <v>32.015003673687488</v>
+      </c>
+      <c r="BA2" s="10">
+        <v>60</v>
+      </c>
+      <c r="BB2" s="10">
+        <v>59.5</v>
+      </c>
+      <c r="BC2" s="10">
+        <v>25.3</v>
+      </c>
+      <c r="BD2" s="10">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="BE2" s="10">
+        <v>71.400000000000006</v>
+      </c>
+    </row>
+    <row r="3" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="1">
+        <v>112</v>
+      </c>
+      <c r="C3" s="1">
+        <v>58.5</v>
+      </c>
+      <c r="D3" s="1">
+        <v>3.9379241252113077</v>
+      </c>
+      <c r="E3" s="1">
+        <v>10.8</v>
+      </c>
+      <c r="F3" s="1">
+        <v>99.506</v>
+      </c>
+      <c r="G3" s="1">
+        <v>99.91</v>
+      </c>
+      <c r="H3" s="2">
+        <v>903</v>
+      </c>
+      <c r="I3" s="2">
+        <v>13.475914213704883</v>
+      </c>
+      <c r="J3" s="2">
+        <v>28.6</v>
+      </c>
+      <c r="K3" s="2">
+        <v>82.8</v>
+      </c>
+      <c r="L3" s="3">
+        <v>72.843000000000004</v>
+      </c>
+      <c r="M3" s="3">
+        <v>115.9</v>
+      </c>
+      <c r="N3" s="3">
+        <v>45.111000000000004</v>
+      </c>
+      <c r="O3" s="3">
+        <v>85</v>
+      </c>
+      <c r="P3" s="3">
+        <v>77.107799999999997</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>42</v>
+      </c>
+      <c r="R3" s="4">
+        <v>96.12</v>
+      </c>
+      <c r="S3" s="4">
+        <v>154.19485866904074</v>
+      </c>
+      <c r="T3" s="4">
+        <v>114.34898731359893</v>
+      </c>
+      <c r="U3" s="4">
+        <v>68.506565768973957</v>
+      </c>
+      <c r="V3" s="4">
+        <v>110.00000000000001</v>
+      </c>
+      <c r="W3" s="4">
+        <v>81.790000000000006</v>
+      </c>
+      <c r="X3" s="4">
+        <v>171.26641442243491</v>
+      </c>
+      <c r="Y3" s="4">
+        <v>6.7</v>
+      </c>
+      <c r="Z3" s="4">
+        <v>58.978167868485158</v>
+      </c>
+      <c r="AA3" s="4">
+        <v>39.478898578809748</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>53.51</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>88.914900000000003</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>31.076000000000001</v>
+      </c>
+      <c r="AE3" s="5">
+        <v>31.010999999999999</v>
+      </c>
+      <c r="AF3" s="5">
+        <v>22.59</v>
+      </c>
+      <c r="AG3" s="5">
+        <v>15.5966</v>
+      </c>
+      <c r="AH3" s="6">
+        <v>19</v>
+      </c>
+      <c r="AI3" s="6">
+        <v>34.308999999999997</v>
+      </c>
+      <c r="AJ3" s="6">
+        <v>34</v>
+      </c>
+      <c r="AK3" s="6">
+        <v>40</v>
+      </c>
+      <c r="AL3" s="6">
+        <v>128.5</v>
+      </c>
+      <c r="AM3" s="20">
+        <v>31.5</v>
+      </c>
+      <c r="AN3" s="20">
+        <v>6.4</v>
+      </c>
+      <c r="AO3" s="20">
+        <v>55.1</v>
+      </c>
+      <c r="AP3" s="20">
+        <v>13.7</v>
+      </c>
+      <c r="AQ3" s="20">
+        <v>29.900000000000002</v>
+      </c>
+      <c r="AR3" s="11">
+        <v>73</v>
+      </c>
+      <c r="AS3" s="11">
+        <v>46</v>
+      </c>
+      <c r="AT3" s="8">
+        <v>16.53</v>
+      </c>
+      <c r="AU3" s="8">
+        <v>23.742000000000001</v>
+      </c>
+      <c r="AV3" s="21">
+        <v>41.3</v>
+      </c>
+      <c r="AW3" s="21">
+        <v>68.072142659479965</v>
+      </c>
+      <c r="AX3" s="21">
+        <v>7.9873670095453182</v>
+      </c>
+      <c r="AY3" s="21">
+        <v>6.7</v>
+      </c>
+      <c r="AZ3" s="21">
+        <v>19.24662479406609</v>
+      </c>
+      <c r="BA3" s="10">
+        <v>59.2</v>
+      </c>
+      <c r="BB3" s="10">
+        <v>59.3</v>
+      </c>
+      <c r="BC3" s="10">
+        <v>20.3</v>
+      </c>
+      <c r="BD3" s="10">
+        <v>72.099999999999994</v>
+      </c>
+      <c r="BE3" s="10">
+        <v>72.099999999999994</v>
+      </c>
+    </row>
+    <row r="4" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="1">
+        <v>81</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46.3</v>
+      </c>
+      <c r="D4" s="1">
+        <v>4.51903680676691</v>
+      </c>
+      <c r="E4" s="1">
+        <v>9.9</v>
+      </c>
+      <c r="F4" s="1">
+        <v>99.509</v>
+      </c>
+      <c r="G4" s="1">
+        <v>99.76</v>
+      </c>
+      <c r="H4" s="2">
+        <v>933</v>
+      </c>
+      <c r="I4" s="2">
+        <v>10.674600022243052</v>
+      </c>
+      <c r="J4" s="2">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="K4" s="2">
+        <v>83.1</v>
+      </c>
+      <c r="L4" s="3">
+        <v>62.533999999999999</v>
+      </c>
+      <c r="M4" s="3">
+        <v>108.4</v>
+      </c>
+      <c r="N4" s="3">
+        <v>34.055</v>
+      </c>
+      <c r="O4" s="3">
+        <v>76</v>
+      </c>
+      <c r="P4" s="3">
+        <v>77.710499999999996</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>44</v>
+      </c>
+      <c r="R4" s="4">
+        <v>52.120000000000005</v>
+      </c>
+      <c r="S4" s="4">
+        <v>147.57264549000874</v>
+      </c>
+      <c r="T4" s="4">
+        <v>97.644295836318761</v>
+      </c>
+      <c r="U4" s="4">
+        <v>53.017275694610305</v>
+      </c>
+      <c r="V4" s="4">
+        <v>140</v>
+      </c>
+      <c r="W4" s="4">
+        <v>60.22</v>
+      </c>
+      <c r="X4" s="4">
+        <v>93.436032163044345</v>
+      </c>
+      <c r="Y4" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>61.802931507816574</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>42.017914051735239</v>
+      </c>
+      <c r="AB4" s="5">
+        <v>37.06</v>
+      </c>
+      <c r="AC4" s="5">
+        <v>84.590400000000002</v>
+      </c>
+      <c r="AD4" s="5">
+        <v>31.847000000000001</v>
+      </c>
+      <c r="AE4" s="5">
+        <v>31.935500000000001</v>
+      </c>
+      <c r="AF4" s="5">
+        <v>22.44</v>
+      </c>
+      <c r="AG4" s="5">
+        <v>18.194200000000002</v>
+      </c>
+      <c r="AH4" s="6">
+        <v>28</v>
+      </c>
+      <c r="AI4" s="6">
+        <v>32.896000000000001</v>
+      </c>
+      <c r="AJ4" s="6">
+        <v>29</v>
+      </c>
+      <c r="AK4" s="6">
+        <v>20</v>
+      </c>
+      <c r="AL4" s="6">
+        <v>158.9</v>
+      </c>
+      <c r="AM4" s="20">
+        <v>38.9</v>
+      </c>
+      <c r="AN4" s="20">
+        <v>10.6</v>
+      </c>
+      <c r="AO4" s="20">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="AP4" s="20">
+        <v>16.7</v>
+      </c>
+      <c r="AQ4" s="20">
+        <v>22.7</v>
+      </c>
+      <c r="AR4" s="11">
+        <v>74</v>
+      </c>
+      <c r="AS4" s="11">
+        <v>35</v>
+      </c>
+      <c r="AT4" s="8">
+        <v>13.52</v>
+      </c>
+      <c r="AU4" s="8">
+        <v>11.891999999999999</v>
+      </c>
+      <c r="AV4" s="21">
+        <v>41.3</v>
+      </c>
+      <c r="AW4" s="21">
+        <v>71.664539014003523</v>
+      </c>
+      <c r="AX4" s="21">
+        <v>10.927709229464034</v>
+      </c>
+      <c r="AY4" s="21">
+        <v>6.8</v>
+      </c>
+      <c r="AZ4" s="21">
+        <v>9.8119517338624149</v>
+      </c>
+      <c r="BA4" s="10">
+        <v>56.7</v>
+      </c>
+      <c r="BB4" s="10">
+        <v>58.6</v>
+      </c>
+      <c r="BC4" s="10">
+        <v>23.4</v>
+      </c>
+      <c r="BD4" s="10">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="BE4" s="10">
+        <v>73.599999999999994</v>
+      </c>
+    </row>
+    <row r="5" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="1">
+        <v>71</v>
+      </c>
+      <c r="C5" s="1">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4.362735355569388</v>
+      </c>
+      <c r="E5" s="1">
+        <v>10.9</v>
+      </c>
+      <c r="F5" s="1">
+        <v>99.504999999999995</v>
+      </c>
+      <c r="G5" s="1">
+        <v>99.92</v>
+      </c>
+      <c r="H5" s="2">
+        <v>955</v>
+      </c>
+      <c r="I5" s="2">
+        <v>9.4729169863434084</v>
+      </c>
+      <c r="J5" s="2">
+        <v>12.7</v>
+      </c>
+      <c r="K5" s="2">
+        <v>83.1</v>
+      </c>
+      <c r="L5" s="3">
+        <v>72.438000000000002</v>
+      </c>
+      <c r="M5" s="3">
+        <v>138.6</v>
+      </c>
+      <c r="N5" s="3">
+        <v>47.210999999999999</v>
+      </c>
+      <c r="O5" s="3">
+        <v>102</v>
+      </c>
+      <c r="P5" s="3">
+        <v>78.871899999999997</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>42</v>
+      </c>
+      <c r="R5" s="4">
+        <v>65.69</v>
+      </c>
+      <c r="S5" s="4">
+        <v>106.49199313697454</v>
+      </c>
+      <c r="T5" s="4">
+        <v>63.692450672004576</v>
+      </c>
+      <c r="U5" s="4">
+        <v>27.24478124106377</v>
+      </c>
+      <c r="V5" s="4">
+        <v>190</v>
+      </c>
+      <c r="W5" s="4">
+        <v>45.36</v>
+      </c>
+      <c r="X5" s="4">
+        <v>108.48584501000857</v>
+      </c>
+      <c r="Y5" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="Z5" s="4">
+        <v>66.350024563523121</v>
+      </c>
+      <c r="AA5" s="4">
+        <v>47.383497620056147</v>
+      </c>
+      <c r="AB5" s="5">
+        <v>60.13</v>
+      </c>
+      <c r="AC5" s="5">
+        <v>89.232000000000014</v>
+      </c>
+      <c r="AD5" s="5">
+        <v>33.058999999999997</v>
+      </c>
+      <c r="AE5" s="5">
+        <v>31.1036</v>
+      </c>
+      <c r="AF5" s="5">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="AG5" s="5">
+        <v>17.535499999999999</v>
+      </c>
+      <c r="AH5" s="6">
+        <v>24</v>
+      </c>
+      <c r="AI5" s="6">
+        <v>39.229999999999997</v>
+      </c>
+      <c r="AJ5" s="6">
+        <v>44</v>
+      </c>
+      <c r="AK5" s="6">
+        <v>30</v>
+      </c>
+      <c r="AL5" s="6">
+        <v>247</v>
+      </c>
+      <c r="AM5" s="20">
+        <v>25</v>
+      </c>
+      <c r="AN5" s="20">
+        <v>7.9</v>
+      </c>
+      <c r="AO5" s="20">
+        <v>47</v>
+      </c>
+      <c r="AP5" s="20">
+        <v>10.7</v>
+      </c>
+      <c r="AQ5" s="20">
+        <v>13.899999999999999</v>
+      </c>
+      <c r="AR5" s="11">
+        <v>45</v>
+      </c>
+      <c r="AS5" s="11">
+        <v>34</v>
+      </c>
+      <c r="AT5" s="8">
+        <v>18.440000000000001</v>
+      </c>
+      <c r="AU5" s="8">
+        <v>15.087999999999999</v>
+      </c>
+      <c r="AV5" s="21">
+        <v>42.5</v>
+      </c>
+      <c r="AW5" s="21">
+        <v>78.358536459872894</v>
+      </c>
+      <c r="AX5" s="21">
+        <v>12.764234226937718</v>
+      </c>
+      <c r="AY5" s="21">
+        <v>9</v>
+      </c>
+      <c r="AZ5" s="21">
+        <v>23.427695599399264</v>
+      </c>
+      <c r="BA5" s="10">
+        <v>56.6</v>
+      </c>
+      <c r="BB5" s="10">
+        <v>59</v>
+      </c>
+      <c r="BC5" s="10">
+        <v>20</v>
+      </c>
+      <c r="BD5" s="10">
+        <v>72.3</v>
+      </c>
+      <c r="BE5" s="10">
+        <v>72.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="1">
+        <v>132</v>
+      </c>
+      <c r="C6" s="1">
+        <v>62.1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2.5842161469634721</v>
+      </c>
+      <c r="E6" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="F6" s="1">
+        <v>99.355000000000004</v>
+      </c>
+      <c r="G6" s="1">
+        <v>99.94</v>
+      </c>
+      <c r="H6" s="2">
+        <v>961</v>
+      </c>
+      <c r="I6" s="2">
+        <v>11.298931508198336</v>
+      </c>
+      <c r="J6" s="2">
+        <v>29.3</v>
+      </c>
+      <c r="K6" s="2">
+        <v>83.4</v>
+      </c>
+      <c r="L6" s="3">
+        <v>86.150999999999996</v>
+      </c>
+      <c r="M6" s="3">
+        <v>123.6</v>
+      </c>
+      <c r="N6" s="3">
+        <v>48.743000000000002</v>
+      </c>
+      <c r="O6" s="3">
+        <v>85</v>
+      </c>
+      <c r="P6" s="3">
+        <v>80.963200000000001</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>96</v>
+      </c>
+      <c r="R6" s="4">
+        <v>69.95</v>
+      </c>
+      <c r="S6" s="4">
+        <v>139.86936714419014</v>
+      </c>
+      <c r="T6" s="4">
+        <v>117.98013063285579</v>
+      </c>
+      <c r="U6" s="4">
+        <v>72.671387013557279</v>
+      </c>
+      <c r="V6" s="4">
+        <v>150</v>
+      </c>
+      <c r="W6" s="4">
+        <v>86.44</v>
+      </c>
+      <c r="X6" s="4">
+        <v>156.6057412591251</v>
+      </c>
+      <c r="Y6" s="4">
+        <v>6</v>
+      </c>
+      <c r="Z6" s="4">
+        <v>61.91044389484275</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>94.560086077614613</v>
+      </c>
+      <c r="AB6" s="5">
+        <v>52.86</v>
+      </c>
+      <c r="AC6" s="5">
+        <v>90.464400000000012</v>
+      </c>
+      <c r="AD6" s="5">
+        <v>31.974</v>
+      </c>
+      <c r="AE6" s="5">
+        <v>29.409000000000002</v>
+      </c>
+      <c r="AF6" s="5">
+        <v>20.72</v>
+      </c>
+      <c r="AG6" s="5">
+        <v>17.5442</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>19</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>33.125999999999998</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>49</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>30</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>102.7</v>
+      </c>
+      <c r="AM6" s="20">
+        <v>43.1</v>
+      </c>
+      <c r="AN6" s="20">
+        <v>11.6</v>
+      </c>
+      <c r="AO6" s="20">
+        <v>55.5</v>
+      </c>
+      <c r="AP6" s="20">
+        <v>16.7</v>
+      </c>
+      <c r="AQ6" s="20">
+        <v>27</v>
+      </c>
+      <c r="AR6" s="11">
+        <v>54</v>
+      </c>
+      <c r="AS6" s="11">
+        <v>31</v>
+      </c>
+      <c r="AT6" s="8">
+        <v>9.9499999999999993</v>
+      </c>
+      <c r="AU6" s="8">
+        <v>10.904999999999999</v>
+      </c>
+      <c r="AV6" s="21">
+        <v>46.1</v>
+      </c>
+      <c r="AW6" s="21">
+        <v>85.471184747370231</v>
+      </c>
+      <c r="AX6" s="21">
+        <v>10.775555265031013</v>
+      </c>
+      <c r="AY6" s="21">
+        <v>7.8</v>
+      </c>
+      <c r="AZ6" s="21">
+        <v>29.004708735905119</v>
+      </c>
+      <c r="BA6" s="10">
+        <v>56.1</v>
+      </c>
+      <c r="BB6" s="10">
+        <v>57.9</v>
+      </c>
+      <c r="BC6" s="10">
+        <v>23</v>
+      </c>
+      <c r="BD6" s="10">
+        <v>76</v>
+      </c>
+      <c r="BE6" s="10">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="1">
+        <v>226</v>
+      </c>
+      <c r="C7" s="1">
+        <v>48</v>
+      </c>
+      <c r="D7" s="1">
+        <v>4.1760396469417689</v>
+      </c>
+      <c r="E7" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="F7" s="1">
+        <v>99.817999999999998</v>
+      </c>
+      <c r="G7" s="1">
+        <v>100.17</v>
+      </c>
+      <c r="H7" s="2">
+        <v>954</v>
+      </c>
+      <c r="I7" s="2">
+        <v>11.915542441710141</v>
+      </c>
+      <c r="J7" s="2">
+        <v>45.7</v>
+      </c>
+      <c r="K7" s="2">
+        <v>87</v>
+      </c>
+      <c r="L7" s="3">
+        <v>80.975999999999999</v>
+      </c>
+      <c r="M7" s="3">
+        <v>145.6</v>
+      </c>
+      <c r="N7" s="3">
+        <v>54.097999999999999</v>
+      </c>
+      <c r="O7" s="3">
+        <v>109</v>
+      </c>
+      <c r="P7" s="3">
+        <v>88.187099999999987</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>39</v>
+      </c>
+      <c r="R7" s="4">
+        <v>89.27000000000001</v>
+      </c>
+      <c r="S7" s="4">
+        <v>209.70098136073241</v>
+      </c>
+      <c r="T7" s="4">
+        <v>174.25146545478495</v>
+      </c>
+      <c r="U7" s="4">
+        <v>116.14964104590661</v>
+      </c>
+      <c r="V7" s="4">
+        <v>170</v>
+      </c>
+      <c r="W7" s="4">
+        <v>118.01</v>
+      </c>
+      <c r="X7" s="4">
+        <v>58.275703088981096</v>
+      </c>
+      <c r="Y7" s="4">
+        <v>7.1</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>56.933047044114346</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>72.13601925804285</v>
+      </c>
+      <c r="AB7" s="5">
+        <v>49.45</v>
+      </c>
+      <c r="AC7" s="5">
+        <v>87.231800000000007</v>
+      </c>
+      <c r="AD7" s="5">
+        <v>34.686</v>
+      </c>
+      <c r="AE7" s="5">
+        <v>33.231900000000003</v>
+      </c>
+      <c r="AF7" s="5">
+        <v>32.51</v>
+      </c>
+      <c r="AG7" s="5">
+        <v>14.253</v>
+      </c>
+      <c r="AH7" s="6">
+        <v>21</v>
+      </c>
+      <c r="AI7" s="6">
+        <v>33.374000000000002</v>
+      </c>
+      <c r="AJ7" s="6">
+        <v>46</v>
+      </c>
+      <c r="AK7" s="6">
+        <v>70</v>
+      </c>
+      <c r="AL7" s="6">
+        <v>208.1</v>
+      </c>
+      <c r="AM7" s="20">
+        <v>37.1</v>
+      </c>
+      <c r="AN7" s="20">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="AO7" s="20">
+        <v>57.1</v>
+      </c>
+      <c r="AP7" s="20">
+        <v>14.8</v>
+      </c>
+      <c r="AQ7" s="20">
+        <v>21.6</v>
+      </c>
+      <c r="AR7" s="11">
+        <v>41</v>
+      </c>
+      <c r="AS7" s="11">
+        <v>27</v>
+      </c>
+      <c r="AT7" s="8">
+        <v>30.18</v>
+      </c>
+      <c r="AU7" s="8">
+        <v>45.212000000000003</v>
+      </c>
+      <c r="AV7" s="21">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="AW7" s="21">
+        <v>94.971440391924347</v>
+      </c>
+      <c r="AX7" s="21">
+        <v>11.593814419830618</v>
+      </c>
+      <c r="AY7" s="21">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="AZ7" s="21">
+        <v>8.7658196015085927</v>
+      </c>
+      <c r="BA7" s="10">
+        <v>59.3</v>
+      </c>
+      <c r="BB7" s="10">
+        <v>60.2</v>
+      </c>
+      <c r="BC7" s="10">
+        <v>25.6</v>
+      </c>
+      <c r="BD7" s="10">
+        <v>68.900000000000006</v>
+      </c>
+      <c r="BE7" s="10">
+        <v>68.900000000000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="1">
+        <v>155</v>
+      </c>
+      <c r="C8" s="1">
+        <v>64.7</v>
+      </c>
+      <c r="D8" s="1">
+        <v>2.2331409202932018</v>
+      </c>
+      <c r="E8" s="1">
+        <v>13.2</v>
+      </c>
+      <c r="F8" s="1">
+        <v>99.721999999999994</v>
+      </c>
+      <c r="G8" s="1">
+        <v>100.25</v>
+      </c>
+      <c r="H8" s="2">
+        <v>982</v>
+      </c>
+      <c r="I8" s="2">
+        <v>15.608251387133988</v>
+      </c>
+      <c r="J8" s="2">
+        <v>51.6</v>
+      </c>
+      <c r="K8" s="2">
+        <v>85.5</v>
+      </c>
+      <c r="L8" s="3">
+        <v>142.761</v>
+      </c>
+      <c r="M8" s="3">
+        <v>191.1</v>
+      </c>
+      <c r="N8" s="3">
+        <v>107.70699999999999</v>
+      </c>
+      <c r="O8" s="3">
+        <v>144</v>
+      </c>
+      <c r="P8" s="3">
+        <v>100.18709999999999</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>81</v>
+      </c>
+      <c r="R8" s="4">
+        <v>90.3</v>
+      </c>
+      <c r="S8" s="4">
+        <v>158.40682828055571</v>
+      </c>
+      <c r="T8" s="4">
+        <v>117.73665560492717</v>
+      </c>
+      <c r="U8" s="4">
+        <v>70.265481748129815</v>
+      </c>
+      <c r="V8" s="4">
+        <v>110.00000000000001</v>
+      </c>
+      <c r="W8" s="4">
+        <v>153.68</v>
+      </c>
+      <c r="X8" s="4">
+        <v>197.36768097193317</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>5</v>
+      </c>
+      <c r="Z8" s="4">
+        <v>67.38870892021761</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>52.009544640648713</v>
+      </c>
+      <c r="AB8" s="5">
+        <v>136.87</v>
+      </c>
+      <c r="AC8" s="5">
+        <v>108.43209999999999</v>
+      </c>
+      <c r="AD8" s="5">
+        <v>39.391000000000005</v>
+      </c>
+      <c r="AE8" s="5">
+        <v>38.196199999999997</v>
+      </c>
+      <c r="AF8" s="5">
+        <v>18.489999999999998</v>
+      </c>
+      <c r="AG8" s="5">
+        <v>17.139099999999999</v>
+      </c>
+      <c r="AH8" s="6">
+        <v>17</v>
+      </c>
+      <c r="AI8" s="6">
+        <v>31.914999999999999</v>
+      </c>
+      <c r="AJ8" s="6">
+        <v>57</v>
+      </c>
+      <c r="AK8" s="6">
+        <v>70</v>
+      </c>
+      <c r="AL8" s="6">
+        <v>168</v>
+      </c>
+      <c r="AM8" s="20">
+        <v>52.2</v>
+      </c>
+      <c r="AN8" s="20">
+        <v>12.2</v>
+      </c>
+      <c r="AO8" s="20">
+        <v>63.6</v>
+      </c>
+      <c r="AP8" s="20">
+        <v>16.3</v>
+      </c>
+      <c r="AQ8" s="20">
+        <v>27.9</v>
+      </c>
+      <c r="AR8" s="11">
+        <v>40</v>
+      </c>
+      <c r="AS8" s="11">
+        <v>25</v>
+      </c>
+      <c r="AT8" s="8">
+        <v>13.09</v>
+      </c>
+      <c r="AU8" s="8">
+        <v>20.224</v>
+      </c>
+      <c r="AV8" s="21">
+        <v>46.480000000000004</v>
+      </c>
+      <c r="AW8" s="21">
+        <v>95.622626003703928</v>
+      </c>
+      <c r="AX8" s="21">
+        <v>5.8247130583527209</v>
+      </c>
+      <c r="AY8" s="21">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AZ8" s="21">
+        <v>21.8287676627195</v>
+      </c>
+      <c r="BA8" s="10">
+        <v>63.3</v>
+      </c>
+      <c r="BB8" s="10">
+        <v>59.1</v>
+      </c>
+      <c r="BC8" s="10">
+        <v>32.4</v>
+      </c>
+      <c r="BD8" s="10">
+        <v>70.8</v>
+      </c>
+      <c r="BE8" s="10">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="1">
+        <v>101</v>
+      </c>
+      <c r="C9" s="1">
+        <v>53.2</v>
+      </c>
+      <c r="D9" s="1">
+        <v>5.7863002327767719</v>
+      </c>
+      <c r="E9" s="1">
+        <v>9.9</v>
+      </c>
+      <c r="F9" s="1">
+        <v>99.427000000000007</v>
+      </c>
+      <c r="G9" s="1">
+        <v>99.88</v>
+      </c>
+      <c r="H9" s="2">
+        <v>980</v>
+      </c>
+      <c r="I9" s="2">
+        <v>13.967230034834214</v>
+      </c>
+      <c r="J9" s="2">
+        <v>23.3</v>
+      </c>
+      <c r="K9" s="2">
+        <v>81</v>
+      </c>
+      <c r="L9" s="3">
+        <v>72.962999999999994</v>
+      </c>
+      <c r="M9" s="3">
+        <v>123.2</v>
+      </c>
+      <c r="N9" s="3">
+        <v>46.991</v>
+      </c>
+      <c r="O9" s="3">
+        <v>71</v>
+      </c>
+      <c r="P9" s="3">
+        <v>79.583500000000001</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>8</v>
+      </c>
+      <c r="R9" s="4">
+        <v>73.010000000000005</v>
+      </c>
+      <c r="S9" s="4">
+        <v>110.59817254568635</v>
+      </c>
+      <c r="T9" s="4">
+        <v>91.755206119847003</v>
+      </c>
+      <c r="U9" s="4">
+        <v>50.849978750531236</v>
+      </c>
+      <c r="V9" s="4">
+        <v>90</v>
+      </c>
+      <c r="W9" s="4">
+        <v>29.91</v>
+      </c>
+      <c r="X9" s="4">
+        <v>147.09944751381215</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>62.151538605247005</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>52.736929194801036</v>
+      </c>
+      <c r="AB9" s="5">
+        <v>71.97</v>
+      </c>
+      <c r="AC9" s="5">
+        <v>86.182900000000004</v>
+      </c>
+      <c r="AD9" s="5">
+        <v>33.792000000000002</v>
+      </c>
+      <c r="AE9" s="5">
+        <v>30.395399999999999</v>
+      </c>
+      <c r="AF9" s="5">
+        <v>14.94</v>
+      </c>
+      <c r="AG9" s="5">
+        <v>14.173900000000001</v>
+      </c>
+      <c r="AH9" s="6">
+        <v>32</v>
+      </c>
+      <c r="AI9" s="6">
+        <v>39.35</v>
+      </c>
+      <c r="AJ9" s="6">
+        <v>50</v>
+      </c>
+      <c r="AK9" s="6">
+        <v>30</v>
+      </c>
+      <c r="AL9" s="6">
+        <v>95.8</v>
+      </c>
+      <c r="AM9" s="20">
+        <v>25.7</v>
+      </c>
+      <c r="AN9" s="20">
+        <v>7.2</v>
+      </c>
+      <c r="AO9" s="20">
+        <v>55.4</v>
+      </c>
+      <c r="AP9" s="20">
+        <v>12.9</v>
+      </c>
+      <c r="AQ9" s="20">
+        <v>27.200000000000003</v>
+      </c>
+      <c r="AR9" s="11">
+        <v>59</v>
+      </c>
+      <c r="AS9" s="11">
+        <v>29</v>
+      </c>
+      <c r="AT9" s="8">
+        <v>8.4600000000000009</v>
+      </c>
+      <c r="AU9" s="8">
+        <v>8.2729999999999997</v>
+      </c>
+      <c r="AV9" s="21">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="AW9" s="21">
+        <v>102.19749238313737</v>
+      </c>
+      <c r="AX9" s="21">
+        <v>11.911139848512839</v>
+      </c>
+      <c r="AY9" s="21">
+        <v>10.6</v>
+      </c>
+      <c r="AZ9" s="21">
+        <v>20.967505188305768</v>
+      </c>
+      <c r="BA9" s="10">
+        <v>59.5</v>
+      </c>
+      <c r="BB9" s="10">
+        <v>60.3</v>
+      </c>
+      <c r="BC9" s="10">
+        <v>20.7</v>
+      </c>
+      <c r="BD9" s="10">
+        <v>70.5</v>
+      </c>
+      <c r="BE9" s="10">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="1">
+        <v>117</v>
+      </c>
+      <c r="C10" s="1">
+        <v>41.3</v>
+      </c>
+      <c r="D10" s="1">
+        <v>6.4209691596285392</v>
+      </c>
+      <c r="E10" s="1">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="F10" s="1">
+        <v>99.688000000000002</v>
+      </c>
+      <c r="G10" s="1">
+        <v>99.88</v>
+      </c>
+      <c r="H10" s="2">
+        <v>940</v>
+      </c>
+      <c r="I10" s="2">
+        <v>14.720645161290323</v>
+      </c>
+      <c r="J10" s="2">
+        <v>22.1</v>
+      </c>
+      <c r="K10" s="2">
+        <v>84.1</v>
+      </c>
+      <c r="L10" s="3">
+        <v>64.986999999999995</v>
+      </c>
+      <c r="M10" s="3">
+        <v>103.8</v>
+      </c>
+      <c r="N10" s="3">
+        <v>47.335000000000001</v>
+      </c>
+      <c r="O10" s="3">
+        <v>73</v>
+      </c>
+      <c r="P10" s="3">
+        <v>75.146900000000002</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="R10" s="4">
+        <v>49.1</v>
+      </c>
+      <c r="S10" s="4">
+        <v>115.30707161268631</v>
+      </c>
+      <c r="T10" s="4">
+        <v>96.061302252605614</v>
+      </c>
+      <c r="U10" s="4">
+        <v>61.677686876611006</v>
+      </c>
+      <c r="V10" s="4">
+        <v>150</v>
+      </c>
+      <c r="W10" s="4">
+        <v>22.51</v>
+      </c>
+      <c r="X10" s="4">
+        <v>164.32253726325226</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="Z10" s="4">
+        <v>57.54249216576337</v>
+      </c>
+      <c r="AA10" s="4">
+        <v>48.994147733525899</v>
+      </c>
+      <c r="AB10" s="5">
+        <v>45.57</v>
+      </c>
+      <c r="AC10" s="5">
+        <v>85.543500000000009</v>
+      </c>
+      <c r="AD10" s="5">
+        <v>30.73</v>
+      </c>
+      <c r="AE10" s="5">
+        <v>31.215599999999998</v>
+      </c>
+      <c r="AF10" s="5">
+        <v>19.25</v>
+      </c>
+      <c r="AG10" s="5">
+        <v>18.854300000000002</v>
+      </c>
+      <c r="AH10" s="6">
+        <v>32</v>
+      </c>
+      <c r="AI10" s="6">
+        <v>41.321999999999996</v>
+      </c>
+      <c r="AJ10" s="6">
+        <v>38</v>
+      </c>
+      <c r="AK10" s="6">
+        <v>40</v>
+      </c>
+      <c r="AL10" s="6">
+        <v>157.6</v>
+      </c>
+      <c r="AM10" s="20">
+        <v>28.6</v>
+      </c>
+      <c r="AN10" s="20">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="AO10" s="20">
+        <v>65</v>
+      </c>
+      <c r="AP10" s="20">
+        <v>16.8</v>
+      </c>
+      <c r="AQ10" s="20">
+        <v>25.099999999999998</v>
+      </c>
+      <c r="AR10" s="11">
+        <v>87</v>
+      </c>
+      <c r="AS10" s="11">
+        <v>40</v>
+      </c>
+      <c r="AT10" s="8">
+        <v>16.739999999999998</v>
+      </c>
+      <c r="AU10" s="8">
+        <v>17.27</v>
+      </c>
+      <c r="AV10" s="21">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="AW10" s="21">
+        <v>62.717353919058361</v>
+      </c>
+      <c r="AX10" s="21">
+        <v>9.1466888723320334</v>
+      </c>
+      <c r="AY10" s="21">
+        <v>7.2</v>
+      </c>
+      <c r="AZ10" s="21">
+        <v>6.6575106947331557</v>
+      </c>
+      <c r="BA10" s="10">
+        <v>52.7</v>
+      </c>
+      <c r="BB10" s="10">
+        <v>60.1</v>
+      </c>
+      <c r="BC10" s="10">
+        <v>22.2</v>
+      </c>
+      <c r="BD10" s="10">
+        <v>69.8</v>
+      </c>
+      <c r="BE10" s="10">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="1">
+        <v>57</v>
+      </c>
+      <c r="C11" s="1">
+        <v>60.9</v>
+      </c>
+      <c r="D11" s="1">
+        <v>5.9628358036980531</v>
+      </c>
+      <c r="E11" s="1">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F11" s="1">
+        <v>99.608000000000004</v>
+      </c>
+      <c r="G11" s="1">
+        <v>99.89</v>
+      </c>
+      <c r="H11" s="2">
+        <v>946</v>
+      </c>
+      <c r="I11" s="2">
+        <v>11.094423012097831</v>
+      </c>
+      <c r="J11" s="2">
+        <v>26.2</v>
+      </c>
+      <c r="K11" s="2">
+        <v>82.4</v>
+      </c>
+      <c r="L11" s="3">
+        <v>70.078999999999994</v>
+      </c>
+      <c r="M11" s="3">
+        <v>109.3</v>
+      </c>
+      <c r="N11" s="3">
+        <v>39.731000000000002</v>
+      </c>
+      <c r="O11" s="3">
+        <v>76</v>
+      </c>
+      <c r="P11" s="3">
+        <v>78.501599999999996</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>82</v>
+      </c>
+      <c r="R11" s="4">
+        <v>45.6</v>
+      </c>
+      <c r="S11" s="4">
+        <v>135.56893049982662</v>
+      </c>
+      <c r="T11" s="4">
+        <v>76.144053103482449</v>
+      </c>
+      <c r="U11" s="4">
+        <v>36.577995739832566</v>
+      </c>
+      <c r="V11" s="4">
+        <v>110.00000000000001</v>
+      </c>
+      <c r="W11" s="4">
+        <v>56.6</v>
+      </c>
+      <c r="X11" s="4">
+        <v>150.36904938822013</v>
+      </c>
+      <c r="Y11" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>54.756390702643429</v>
+      </c>
+      <c r="AA11" s="4">
+        <v>30.486304884134473</v>
+      </c>
+      <c r="AB11" s="5">
+        <v>37.020000000000003</v>
+      </c>
+      <c r="AC11" s="5">
+        <v>93.295100000000005</v>
+      </c>
+      <c r="AD11" s="5">
+        <v>33.686</v>
+      </c>
+      <c r="AE11" s="5">
+        <v>33.5505</v>
+      </c>
+      <c r="AF11" s="5">
+        <v>22.95</v>
+      </c>
+      <c r="AG11" s="5">
+        <v>22.1999</v>
+      </c>
+      <c r="AH11" s="6">
+        <v>20</v>
+      </c>
+      <c r="AI11" s="6">
+        <v>43.111000000000004</v>
+      </c>
+      <c r="AJ11" s="6">
+        <v>37</v>
+      </c>
+      <c r="AK11" s="6">
+        <v>40</v>
+      </c>
+      <c r="AL11" s="6">
+        <v>155.69999999999999</v>
+      </c>
+      <c r="AM11" s="20">
+        <v>41.4</v>
+      </c>
+      <c r="AN11" s="20">
+        <v>11.1</v>
+      </c>
+      <c r="AO11" s="20">
+        <v>63.2</v>
+      </c>
+      <c r="AP11" s="20">
+        <v>16.8</v>
+      </c>
+      <c r="AQ11" s="20">
+        <v>24.5</v>
+      </c>
+      <c r="AR11" s="11">
+        <v>70</v>
+      </c>
+      <c r="AS11" s="11">
+        <v>43</v>
+      </c>
+      <c r="AT11" s="8">
+        <v>12.73</v>
+      </c>
+      <c r="AU11" s="8">
+        <v>11.273999999999999</v>
+      </c>
+      <c r="AV11" s="21">
+        <v>42.5</v>
+      </c>
+      <c r="AW11" s="21">
+        <v>61.943214965480728</v>
+      </c>
+      <c r="AX11" s="21">
+        <v>11.866581141757537</v>
+      </c>
+      <c r="AY11" s="21">
+        <v>6.1</v>
+      </c>
+      <c r="AZ11" s="21">
+        <v>11.459644591574532</v>
+      </c>
+      <c r="BA11" s="10">
+        <v>56.1</v>
+      </c>
+      <c r="BB11" s="10">
+        <v>59.6</v>
+      </c>
+      <c r="BC11" s="10">
+        <v>23.8</v>
+      </c>
+      <c r="BD11" s="10">
+        <v>72.099999999999994</v>
+      </c>
+      <c r="BE11" s="10">
+        <v>72.099999999999994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>104</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="B12" s="1">
+        <v>129</v>
+      </c>
+      <c r="C12" s="1">
+        <v>63.1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>3.7803522644358849</v>
+      </c>
+      <c r="E12" s="1">
+        <v>13.8</v>
+      </c>
+      <c r="F12" s="1">
+        <v>99.753</v>
+      </c>
+      <c r="G12" s="1">
+        <v>100.23</v>
+      </c>
+      <c r="H12" s="2">
+        <v>921</v>
+      </c>
+      <c r="I12" s="2">
+        <v>15.089281462787486</v>
+      </c>
+      <c r="J12" s="2">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="K12" s="2">
+        <v>83.1</v>
+      </c>
+      <c r="L12" s="3">
+        <v>86.643000000000001</v>
+      </c>
+      <c r="M12" s="3">
+        <v>156.69999999999999</v>
+      </c>
+      <c r="N12" s="3">
+        <v>60.132000000000005</v>
+      </c>
+      <c r="O12" s="3">
+        <v>121</v>
+      </c>
+      <c r="P12" s="3">
+        <v>86.202800000000011</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>179</v>
+      </c>
+      <c r="R12" s="4">
+        <v>93.039999999999992</v>
+      </c>
+      <c r="S12" s="4">
+        <v>114.598033861278</v>
+      </c>
+      <c r="T12" s="4">
+        <v>84.502457673402503</v>
+      </c>
+      <c r="U12" s="4">
+        <v>59.098853085745496</v>
+      </c>
+      <c r="V12" s="4">
+        <v>140</v>
+      </c>
+      <c r="W12" s="4">
+        <v>124.78</v>
+      </c>
+      <c r="X12" s="4">
+        <v>159.26815947569634</v>
+      </c>
+      <c r="Y12" s="4">
+        <v>6.4</v>
+      </c>
+      <c r="Z12" s="4">
+        <v>58.379461029601543</v>
+      </c>
+      <c r="AA12" s="4">
+        <v>71.453606224516037</v>
+      </c>
+      <c r="AB12" s="5">
+        <v>74.56</v>
+      </c>
+      <c r="AC12" s="5">
+        <v>92.577500000000001</v>
+      </c>
+      <c r="AD12" s="5">
+        <v>29.987000000000002</v>
+      </c>
+      <c r="AE12" s="5">
+        <v>33.622</v>
+      </c>
+      <c r="AF12" s="5">
+        <v>10.86</v>
+      </c>
+      <c r="AG12" s="5">
+        <v>14.0022</v>
+      </c>
+      <c r="AH12" s="6">
+        <v>13</v>
+      </c>
+      <c r="AI12" s="6">
+        <v>20.879000000000001</v>
+      </c>
+      <c r="AJ12" s="6">
+        <v>54</v>
+      </c>
+      <c r="AK12" s="6">
+        <v>40</v>
+      </c>
+      <c r="AL12" s="6">
+        <v>158.30000000000001</v>
+      </c>
+      <c r="AM12" s="20">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="AN12" s="20">
+        <v>10.1</v>
+      </c>
+      <c r="AO12" s="20">
+        <v>45.8</v>
+      </c>
+      <c r="AP12" s="20">
+        <v>12</v>
+      </c>
+      <c r="AQ12" s="20">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="AR12" s="11">
+        <v>46</v>
+      </c>
+      <c r="AS12" s="11">
         <v>33</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AT12" s="8">
+        <v>49.07</v>
+      </c>
+      <c r="AU12" s="8">
+        <v>46.250999999999998</v>
+      </c>
+      <c r="AV12" s="21">
+        <v>42.5</v>
+      </c>
+      <c r="AW12" s="21">
+        <v>87.357677362428518</v>
+      </c>
+      <c r="AX12" s="21">
+        <v>8.275216426309866</v>
+      </c>
+      <c r="AY12" s="21">
+        <v>6.3</v>
+      </c>
+      <c r="AZ12" s="21">
+        <v>19.88638771231328</v>
+      </c>
+      <c r="BA12" s="10">
+        <v>60.1</v>
+      </c>
+      <c r="BB12" s="10">
+        <v>59.6</v>
+      </c>
+      <c r="BC12" s="10">
+        <v>25.4</v>
+      </c>
+      <c r="BD12" s="10">
+        <v>70.3</v>
+      </c>
+      <c r="BE12" s="10">
+        <v>70.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="1">
+        <v>355</v>
+      </c>
+      <c r="C13" s="1">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="D13" s="1">
+        <v>3.1418935032194324</v>
+      </c>
+      <c r="E13" s="1">
+        <v>9.6</v>
+      </c>
+      <c r="F13" s="1">
+        <v>99.394999999999996</v>
+      </c>
+      <c r="G13" s="1">
+        <v>99.93</v>
+      </c>
+      <c r="H13" s="2">
+        <v>974</v>
+      </c>
+      <c r="I13" s="2">
+        <v>14.224033639107812</v>
+      </c>
+      <c r="J13" s="2">
+        <v>28.2</v>
+      </c>
+      <c r="K13" s="2">
+        <v>84.3</v>
+      </c>
+      <c r="L13" s="3">
+        <v>93.590999999999994</v>
+      </c>
+      <c r="M13" s="3">
+        <v>127.1</v>
+      </c>
+      <c r="N13" s="3">
+        <v>54.097999999999999</v>
+      </c>
+      <c r="O13" s="3">
+        <v>82</v>
+      </c>
+      <c r="P13" s="3">
+        <v>85.375400000000013</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>176</v>
+      </c>
+      <c r="R13" s="4">
+        <v>132.32</v>
+      </c>
+      <c r="S13" s="4">
+        <v>198.9751074353361</v>
+      </c>
+      <c r="T13" s="4">
+        <v>177.07370469472147</v>
+      </c>
+      <c r="U13" s="4">
+        <v>121.92491688964567</v>
+      </c>
+      <c r="V13" s="4">
+        <v>320</v>
+      </c>
+      <c r="W13" s="4">
+        <v>79.680000000000007</v>
+      </c>
+      <c r="X13" s="4">
+        <v>73.826319630260272</v>
+      </c>
+      <c r="Y13" s="4">
+        <v>15.3</v>
+      </c>
+      <c r="Z13" s="4">
+        <v>58.370118491804647</v>
+      </c>
+      <c r="AA13" s="4">
+        <v>41.34134852423422</v>
+      </c>
+      <c r="AB13" s="5">
+        <v>76.150000000000006</v>
+      </c>
+      <c r="AC13" s="5">
+        <v>89.872299999999996</v>
+      </c>
+      <c r="AD13" s="5">
+        <v>27.011000000000003</v>
+      </c>
+      <c r="AE13" s="5">
+        <v>34.023000000000003</v>
+      </c>
+      <c r="AF13" s="5">
+        <v>24.06</v>
+      </c>
+      <c r="AG13" s="5">
+        <v>12.795499999999999</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>17</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>34.786999999999999</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>55</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>40</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>153.1</v>
+      </c>
+      <c r="AM13" s="20">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="AN13" s="20">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="AO13" s="20">
+        <v>60.9</v>
+      </c>
+      <c r="AP13" s="20">
+        <v>14.2</v>
+      </c>
+      <c r="AQ13" s="20">
+        <v>24.6</v>
+      </c>
+      <c r="AR13" s="11">
+        <v>36</v>
+      </c>
+      <c r="AS13" s="11">
+        <v>22</v>
+      </c>
+      <c r="AT13" s="8">
+        <v>11.24</v>
+      </c>
+      <c r="AU13" s="8">
+        <v>14.305</v>
+      </c>
+      <c r="AV13" s="21">
+        <v>44.5</v>
+      </c>
+      <c r="AW13" s="21">
+        <v>72.480950271976738</v>
+      </c>
+      <c r="AX13" s="21">
+        <v>7.7364535680665885</v>
+      </c>
+      <c r="AY13" s="21">
+        <v>6</v>
+      </c>
+      <c r="AZ13" s="21">
+        <v>34.195514835105868</v>
+      </c>
+      <c r="BA13" s="10">
+        <v>55.9</v>
+      </c>
+      <c r="BB13" s="10">
+        <v>58.9</v>
+      </c>
+      <c r="BC13" s="10">
+        <v>22.8</v>
+      </c>
+      <c r="BD13" s="10">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="BE13" s="10">
+        <v>73.599999999999994</v>
+      </c>
+    </row>
+    <row r="14" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="1">
+        <v>101</v>
+      </c>
+      <c r="C14" s="1">
+        <v>45</v>
+      </c>
+      <c r="D14" s="1">
+        <v>4.5242307721236852</v>
+      </c>
+      <c r="E14" s="1">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="F14" s="1">
+        <v>99.331000000000003</v>
+      </c>
+      <c r="G14" s="1">
+        <v>99.77</v>
+      </c>
+      <c r="H14" s="2">
+        <v>934</v>
+      </c>
+      <c r="I14" s="2">
+        <v>12.972480777013356</v>
+      </c>
+      <c r="J14" s="2">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="K14" s="2">
+        <v>85.8</v>
+      </c>
+      <c r="L14" s="3">
+        <v>67.846999999999994</v>
+      </c>
+      <c r="M14" s="3">
+        <v>114</v>
+      </c>
+      <c r="N14" s="3">
+        <v>38.976999999999997</v>
+      </c>
+      <c r="O14" s="3">
+        <v>76</v>
+      </c>
+      <c r="P14" s="3">
+        <v>76.641800000000003</v>
+      </c>
+      <c r="Q14" s="4">
         <v>48</v>
       </c>
-      <c r="AV1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AX1" t="s">
+      <c r="R14" s="4">
+        <v>46.019999999999996</v>
+      </c>
+      <c r="S14" s="4">
+        <v>146.90120399624286</v>
+      </c>
+      <c r="T14" s="4">
+        <v>126.90888907864399</v>
+      </c>
+      <c r="U14" s="4">
+        <v>119.95559730168218</v>
+      </c>
+      <c r="V14" s="4">
+        <v>130</v>
+      </c>
+      <c r="W14" s="4">
+        <v>41.18</v>
+      </c>
+      <c r="X14" s="4">
+        <v>131.96140380838528</v>
+      </c>
+      <c r="Y14" s="4">
+        <v>6.2</v>
+      </c>
+      <c r="Z14" s="4">
+        <v>57.350241634781028</v>
+      </c>
+      <c r="AA14" s="4">
+        <v>56.910617809685753</v>
+      </c>
+      <c r="AB14" s="5">
+        <v>39.08</v>
+      </c>
+      <c r="AC14" s="5">
+        <v>82.396900000000002</v>
+      </c>
+      <c r="AD14" s="5">
+        <v>31.055</v>
+      </c>
+      <c r="AE14" s="5">
+        <v>27.680300000000003</v>
+      </c>
+      <c r="AF14" s="5">
+        <v>22.42</v>
+      </c>
+      <c r="AG14" s="5">
+        <v>15.6754</v>
+      </c>
+      <c r="AH14" s="6">
+        <v>22</v>
+      </c>
+      <c r="AI14" s="6">
+        <v>36.57</v>
+      </c>
+      <c r="AJ14" s="6">
+        <v>32</v>
+      </c>
+      <c r="AK14" s="6">
+        <v>30</v>
+      </c>
+      <c r="AL14" s="6">
+        <v>146.1</v>
+      </c>
+      <c r="AM14" s="20">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="AN14" s="20">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="AO14" s="20">
+        <v>70.2</v>
+      </c>
+      <c r="AP14" s="20">
+        <v>16</v>
+      </c>
+      <c r="AQ14" s="20">
+        <v>23.599999999999998</v>
+      </c>
+      <c r="AR14" s="11">
+        <v>76</v>
+      </c>
+      <c r="AS14" s="11">
+        <v>43</v>
+      </c>
+      <c r="AT14" s="8">
+        <v>16.579999999999998</v>
+      </c>
+      <c r="AU14" s="8">
+        <v>17.579999999999998</v>
+      </c>
+      <c r="AV14" s="21">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="AW14" s="21">
+        <v>76.828767873156067</v>
+      </c>
+      <c r="AX14" s="21">
+        <v>11.4646700982686</v>
+      </c>
+      <c r="AY14" s="21">
+        <v>6.2</v>
+      </c>
+      <c r="AZ14" s="21">
+        <v>9.0790979543439772</v>
+      </c>
+      <c r="BA14" s="10">
+        <v>55.5</v>
+      </c>
+      <c r="BB14" s="10">
+        <v>58.3</v>
+      </c>
+      <c r="BC14" s="10">
+        <v>22.8</v>
+      </c>
+      <c r="BD14" s="10">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="BE14" s="10">
+        <v>75.599999999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" s="1">
         <v>57</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="C15" s="1">
+        <v>59.3</v>
+      </c>
+      <c r="D15" s="1">
+        <v>5.3130010012790905</v>
+      </c>
+      <c r="E15" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="F15" s="1">
+        <v>99.528999999999996</v>
+      </c>
+      <c r="G15" s="1">
+        <v>99.82</v>
+      </c>
+      <c r="H15" s="2">
+        <v>903</v>
+      </c>
+      <c r="I15" s="2">
+        <v>11.237521099590065</v>
+      </c>
+      <c r="J15" s="2">
+        <v>17.3</v>
+      </c>
+      <c r="K15" s="2">
+        <v>84.4</v>
+      </c>
+      <c r="L15" s="3">
+        <v>64.076999999999998</v>
+      </c>
+      <c r="M15" s="3">
+        <v>111.3</v>
+      </c>
+      <c r="N15" s="3">
+        <v>33.227999999999994</v>
+      </c>
+      <c r="O15" s="3">
+        <v>78</v>
+      </c>
+      <c r="P15" s="3">
+        <v>75.2941</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0</v>
+      </c>
+      <c r="R15" s="4">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="S15" s="4">
+        <v>92.26823315269101</v>
+      </c>
+      <c r="T15" s="4">
+        <v>61.229884581971625</v>
+      </c>
+      <c r="U15" s="4">
+        <v>32.900343358292311</v>
+      </c>
+      <c r="V15" s="4">
+        <v>110.00000000000001</v>
+      </c>
+      <c r="W15" s="4">
+        <v>47.76</v>
+      </c>
+      <c r="X15" s="4">
+        <v>85.363835684441312</v>
+      </c>
+      <c r="Y15" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Z15" s="4">
+        <v>56.554116252181664</v>
+      </c>
+      <c r="AA15" s="4">
+        <v>55.821077980131236</v>
+      </c>
+      <c r="AB15" s="5">
+        <v>38.619999999999997</v>
+      </c>
+      <c r="AC15" s="5">
+        <v>83.757300000000001</v>
+      </c>
+      <c r="AD15" s="5">
+        <v>33.107999999999997</v>
+      </c>
+      <c r="AE15" s="5">
+        <v>28.727699999999999</v>
+      </c>
+      <c r="AF15" s="5">
+        <v>11.33</v>
+      </c>
+      <c r="AG15" s="5">
+        <v>15.756500000000001</v>
+      </c>
+      <c r="AH15" s="6">
+        <v>21</v>
+      </c>
+      <c r="AI15" s="6">
+        <v>28.391999999999999</v>
+      </c>
+      <c r="AJ15" s="6">
+        <v>45</v>
+      </c>
+      <c r="AK15" s="6">
+        <v>30</v>
+      </c>
+      <c r="AL15" s="6">
+        <v>241.2</v>
+      </c>
+      <c r="AM15" s="20">
+        <v>26.4</v>
+      </c>
+      <c r="AN15" s="20">
+        <v>7.1</v>
+      </c>
+      <c r="AO15" s="20">
+        <v>53</v>
+      </c>
+      <c r="AP15" s="20">
+        <v>12.2</v>
+      </c>
+      <c r="AQ15" s="20">
+        <v>17.3</v>
+      </c>
+      <c r="AR15" s="11">
+        <v>84</v>
+      </c>
+      <c r="AS15" s="11">
+        <v>52</v>
+      </c>
+      <c r="AT15" s="8">
+        <v>30.84</v>
+      </c>
+      <c r="AU15" s="8">
+        <v>25.722999999999999</v>
+      </c>
+      <c r="AV15" s="21">
+        <v>41.3</v>
+      </c>
+      <c r="AW15" s="21">
+        <v>69.402242170634153</v>
+      </c>
+      <c r="AX15" s="21">
+        <v>9.0039054117849009</v>
+      </c>
+      <c r="AY15" s="21">
+        <v>8.6</v>
+      </c>
+      <c r="AZ15" s="21">
+        <v>17.717940495384127</v>
+      </c>
+      <c r="BA15" s="10">
+        <v>54.3</v>
+      </c>
+      <c r="BB15" s="10">
+        <v>59.9</v>
+      </c>
+      <c r="BC15" s="10">
+        <v>20.2</v>
+      </c>
+      <c r="BD15" s="10">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="BE15" s="10">
+        <v>70.900000000000006</v>
+      </c>
+    </row>
+    <row r="16" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="1">
+        <v>117</v>
+      </c>
+      <c r="C16" s="1">
+        <v>53.8</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2.5928364006061786</v>
+      </c>
+      <c r="E16" s="1">
+        <v>13.4</v>
+      </c>
+      <c r="F16" s="1">
+        <v>99.72</v>
+      </c>
+      <c r="G16" s="1">
+        <v>100.06</v>
+      </c>
+      <c r="H16" s="2">
+        <v>966</v>
+      </c>
+      <c r="I16" s="2">
+        <v>12.532474741867436</v>
+      </c>
+      <c r="J16" s="2">
+        <v>32.4</v>
+      </c>
+      <c r="K16" s="2">
+        <v>83</v>
+      </c>
+      <c r="L16" s="3">
+        <v>95.103999999999999</v>
+      </c>
+      <c r="M16" s="3">
+        <v>149.1</v>
+      </c>
+      <c r="N16" s="3">
+        <v>59.650999999999996</v>
+      </c>
+      <c r="O16" s="3">
+        <v>105</v>
+      </c>
+      <c r="P16" s="3">
+        <v>77.592200000000005</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>25</v>
+      </c>
+      <c r="R16" s="4">
+        <v>102.67</v>
+      </c>
+      <c r="S16" s="4">
+        <v>138.02521290149534</v>
+      </c>
+      <c r="T16" s="4">
+        <v>104.93126802118957</v>
+      </c>
+      <c r="U16" s="4">
+        <v>58.060081807818683</v>
+      </c>
+      <c r="V16" s="4">
+        <v>190</v>
+      </c>
+      <c r="W16" s="4">
+        <v>90.44</v>
+      </c>
+      <c r="X16" s="4">
+        <v>117.66244216455442</v>
+      </c>
+      <c r="Y16" s="4">
+        <v>6.4</v>
+      </c>
+      <c r="Z16" s="4">
+        <v>65.63233144293261</v>
+      </c>
+      <c r="AA16" s="4">
+        <v>70.786098401564459</v>
+      </c>
+      <c r="AB16" s="5">
+        <v>68.94</v>
+      </c>
+      <c r="AC16" s="5">
+        <v>86.040400000000005</v>
+      </c>
+      <c r="AD16" s="5">
+        <v>30.481999999999999</v>
+      </c>
+      <c r="AE16" s="5">
+        <v>33.453400000000002</v>
+      </c>
+      <c r="AF16" s="5">
+        <v>21.1</v>
+      </c>
+      <c r="AG16" s="5">
+        <v>15.574999999999999</v>
+      </c>
+      <c r="AH16" s="6">
+        <v>18</v>
+      </c>
+      <c r="AI16" s="6">
+        <v>32.786999999999999</v>
+      </c>
+      <c r="AJ16" s="6">
+        <v>41</v>
+      </c>
+      <c r="AK16" s="6">
+        <v>30</v>
+      </c>
+      <c r="AL16" s="6">
+        <v>120.5</v>
+      </c>
+      <c r="AM16" s="20">
+        <v>30.7</v>
+      </c>
+      <c r="AN16" s="20">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="AO16" s="20">
+        <v>48</v>
+      </c>
+      <c r="AP16" s="20">
+        <v>15.4</v>
+      </c>
+      <c r="AQ16" s="20">
+        <v>19.099999999999998</v>
+      </c>
+      <c r="AR16" s="11">
+        <v>29</v>
+      </c>
+      <c r="AS16" s="11">
+        <v>30</v>
+      </c>
+      <c r="AT16" s="8">
+        <v>11.66</v>
+      </c>
+      <c r="AU16" s="8">
+        <v>11.057</v>
+      </c>
+      <c r="AV16" s="21">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="AW16" s="21">
+        <v>69.195187210789086</v>
+      </c>
+      <c r="AX16" s="21">
+        <v>8.1626506024096379</v>
+      </c>
+      <c r="AY16" s="21">
+        <v>4.3</v>
+      </c>
+      <c r="AZ16" s="21">
+        <v>13.392545786278941</v>
+      </c>
+      <c r="BA16" s="10">
+        <v>59.9</v>
+      </c>
+      <c r="BB16" s="10">
+        <v>59.6</v>
+      </c>
+      <c r="BC16" s="10">
+        <v>23.1</v>
+      </c>
+      <c r="BD16" s="10">
+        <v>70.5</v>
+      </c>
+      <c r="BE16" s="10">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="1">
+        <v>72</v>
+      </c>
+      <c r="C17" s="1">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="D17" s="1">
+        <v>4.6134561046644897</v>
+      </c>
+      <c r="E17" s="1">
+        <v>10.8</v>
+      </c>
+      <c r="F17" s="1">
+        <v>99.435000000000002</v>
+      </c>
+      <c r="G17" s="1">
+        <v>99.99</v>
+      </c>
+      <c r="H17" s="2">
+        <v>932</v>
+      </c>
+      <c r="I17" s="2">
+        <v>10.729815455594002</v>
+      </c>
+      <c r="J17" s="2">
+        <v>22.9</v>
+      </c>
+      <c r="K17" s="2">
+        <v>82.7</v>
+      </c>
+      <c r="L17" s="3">
+        <v>74.397999999999996</v>
+      </c>
+      <c r="M17" s="3">
+        <v>157.19999999999999</v>
+      </c>
+      <c r="N17" s="3">
+        <v>49.03</v>
+      </c>
+      <c r="O17" s="3">
+        <v>104</v>
+      </c>
+      <c r="P17" s="3">
+        <v>80.273700000000005</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>87</v>
+      </c>
+      <c r="R17" s="4">
+        <v>59.179999999999993</v>
+      </c>
+      <c r="S17" s="4">
+        <v>81.585269963305961</v>
+      </c>
+      <c r="T17" s="4">
+        <v>62.027782631486986</v>
+      </c>
+      <c r="U17" s="4">
+        <v>32.998427398217721</v>
+      </c>
+      <c r="V17" s="4">
+        <v>140</v>
+      </c>
+      <c r="W17" s="4">
+        <v>117.13</v>
+      </c>
+      <c r="X17" s="4">
+        <v>129.25912982701379</v>
+      </c>
+      <c r="Y17" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="Z17" s="4">
+        <v>57.697158447441574</v>
+      </c>
+      <c r="AA17" s="4">
+        <v>45.778117692047473</v>
+      </c>
+      <c r="AB17" s="5">
+        <v>53.31</v>
+      </c>
+      <c r="AC17" s="5">
+        <v>90.443100000000001</v>
+      </c>
+      <c r="AD17" s="5">
+        <v>35.904000000000003</v>
+      </c>
+      <c r="AE17" s="5">
+        <v>29.017199999999999</v>
+      </c>
+      <c r="AF17" s="5">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="AG17" s="5">
+        <v>16.5563</v>
+      </c>
+      <c r="AH17" s="6">
+        <v>21</v>
+      </c>
+      <c r="AI17" s="6">
+        <v>36.329000000000001</v>
+      </c>
+      <c r="AJ17" s="6">
         <v>60</v>
       </c>
-      <c r="AZ1" t="s">
-        <v>63</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>66</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>78</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>117</v>
+      <c r="AK17" s="6">
+        <v>30</v>
+      </c>
+      <c r="AL17" s="6">
+        <v>175.5</v>
+      </c>
+      <c r="AM17" s="20">
+        <v>34</v>
+      </c>
+      <c r="AN17" s="20">
+        <v>10.7</v>
+      </c>
+      <c r="AO17" s="20">
+        <v>48.1</v>
+      </c>
+      <c r="AP17" s="20">
+        <v>12.6</v>
+      </c>
+      <c r="AQ17" s="20">
+        <v>15.3</v>
+      </c>
+      <c r="AR17" s="11">
+        <v>68</v>
+      </c>
+      <c r="AS17" s="11">
+        <v>33</v>
+      </c>
+      <c r="AT17" s="8">
+        <v>94.5</v>
+      </c>
+      <c r="AU17" s="8">
+        <v>101.574</v>
+      </c>
+      <c r="AV17" s="21">
+        <v>44.5</v>
+      </c>
+      <c r="AW17" s="21">
+        <v>105.82029732475284</v>
+      </c>
+      <c r="AX17" s="21">
+        <v>18.27954099594206</v>
+      </c>
+      <c r="AY17" s="21">
+        <v>12.3</v>
+      </c>
+      <c r="AZ17" s="21">
+        <v>26.184540186221938</v>
+      </c>
+      <c r="BA17" s="10">
+        <v>58.1</v>
+      </c>
+      <c r="BB17" s="10">
+        <v>59.2</v>
+      </c>
+      <c r="BC17" s="10">
+        <v>22.6</v>
+      </c>
+      <c r="BD17" s="10">
+        <v>72.7</v>
+      </c>
+      <c r="BE17" s="10">
+        <v>72.7</v>
       </c>
     </row>
-    <row r="2" spans="1:58">
-      <c r="A2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B2">
-        <v>2879271</v>
-      </c>
-      <c r="C2">
-        <v>145</v>
-      </c>
-      <c r="D2">
-        <v>68</v>
-      </c>
-      <c r="E2">
-        <v>4.1988106967070049</v>
-      </c>
-      <c r="F2">
-        <v>12.7</v>
-      </c>
-      <c r="G2">
-        <v>99.504000000000005</v>
-      </c>
-      <c r="H2">
-        <v>100.14</v>
-      </c>
-      <c r="I2">
-        <v>964</v>
-      </c>
-      <c r="J2">
-        <v>14.412673879443586</v>
-      </c>
-      <c r="K2">
-        <v>436</v>
-      </c>
-      <c r="L2" s="12"/>
-      <c r="M2">
-        <v>82.6</v>
-      </c>
-      <c r="N2">
-        <v>96997</v>
-      </c>
-      <c r="O2">
-        <v>1589</v>
-      </c>
-      <c r="P2">
-        <v>598.02</v>
-      </c>
-      <c r="Q2">
-        <v>112</v>
-      </c>
-      <c r="R2">
-        <v>8867.4599999999991</v>
-      </c>
-      <c r="S2">
-        <v>0.94</v>
-      </c>
-      <c r="T2">
-        <v>727.1</v>
-      </c>
-      <c r="U2">
-        <v>24632.9</v>
-      </c>
-      <c r="V2">
-        <v>20968.400000000001</v>
-      </c>
-      <c r="W2">
-        <v>12638</v>
-      </c>
-      <c r="X2">
-        <v>1.7</v>
-      </c>
-      <c r="Y2">
-        <v>78.12</v>
-      </c>
-      <c r="Z2">
-        <v>27361</v>
-      </c>
-      <c r="AA2">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="AB2">
-        <v>621.6705548036291</v>
-      </c>
-      <c r="AC2">
-        <v>6.5398498439361905</v>
-      </c>
-      <c r="AD2">
-        <v>7651</v>
-      </c>
-      <c r="AE2">
-        <v>9518.94</v>
-      </c>
-      <c r="AF2">
-        <v>399.79</v>
-      </c>
-      <c r="AG2">
-        <v>3147.59</v>
-      </c>
-      <c r="AH2">
-        <v>17.77</v>
-      </c>
-      <c r="AI2">
-        <v>1637.75</v>
-      </c>
-      <c r="AJ2">
-        <v>2</v>
-      </c>
-      <c r="AK2">
-        <v>2833.3</v>
-      </c>
-      <c r="AL2">
-        <v>4.5</v>
-      </c>
-      <c r="AM2">
-        <v>4</v>
-      </c>
-      <c r="AN2">
-        <v>1665</v>
-      </c>
-      <c r="AO2">
-        <v>39.200000000000003</v>
-      </c>
-      <c r="AP2">
-        <v>10.7</v>
-      </c>
-      <c r="AQ2">
-        <v>55.7</v>
-      </c>
-      <c r="AR2">
-        <v>12.2</v>
-      </c>
-      <c r="AS2">
-        <v>1.83</v>
-      </c>
-      <c r="AT2">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="AU2">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="AV2">
-        <v>29.87</v>
-      </c>
-      <c r="AW2">
-        <v>39160</v>
-      </c>
-      <c r="AX2">
-        <v>463</v>
-      </c>
-      <c r="AY2">
-        <v>0.84343869346007116</v>
-      </c>
-      <c r="AZ2">
-        <v>6.848065303509264</v>
-      </c>
-      <c r="BA2">
-        <v>4.7</v>
-      </c>
-      <c r="BB2">
-        <v>92027</v>
-      </c>
-      <c r="BC2">
-        <v>60</v>
-      </c>
-      <c r="BD2">
-        <v>59.5</v>
-      </c>
-      <c r="BE2">
-        <v>25.3</v>
-      </c>
-      <c r="BF2">
-        <v>71.400000000000006</v>
-      </c>
+    <row r="18" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="K18" s="12"/>
     </row>
-    <row r="3" spans="1:58">
-      <c r="A3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B3">
-        <v>1996003</v>
-      </c>
-      <c r="C3">
-        <v>112</v>
-      </c>
-      <c r="D3">
-        <v>58.5</v>
-      </c>
-      <c r="E3">
-        <v>3.9379241252113077</v>
-      </c>
-      <c r="F3">
-        <v>10.8</v>
-      </c>
-      <c r="G3">
-        <v>99.506</v>
-      </c>
-      <c r="H3">
-        <v>99.91</v>
-      </c>
-      <c r="I3">
-        <v>903</v>
-      </c>
-      <c r="J3">
-        <v>13.475914213704883</v>
-      </c>
-      <c r="K3">
-        <v>286</v>
-      </c>
-      <c r="L3" s="12"/>
-      <c r="M3">
-        <v>82.8</v>
-      </c>
-      <c r="N3">
-        <v>72843</v>
-      </c>
-      <c r="O3">
-        <v>1159</v>
-      </c>
-      <c r="P3">
-        <v>451.11</v>
-      </c>
-      <c r="Q3">
-        <v>85</v>
-      </c>
-      <c r="R3">
-        <v>7710.78</v>
-      </c>
-      <c r="S3">
-        <v>0.42</v>
-      </c>
-      <c r="T3">
-        <v>961.2</v>
-      </c>
-      <c r="U3">
-        <v>27711.9</v>
-      </c>
-      <c r="V3">
-        <v>20550.8</v>
-      </c>
-      <c r="W3">
-        <v>12312</v>
-      </c>
-      <c r="X3">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="Y3">
-        <v>81.790000000000006</v>
-      </c>
-      <c r="Z3">
-        <v>30780</v>
-      </c>
-      <c r="AA3">
-        <v>6.7</v>
-      </c>
-      <c r="AB3">
-        <v>589.78167868485161</v>
-      </c>
-      <c r="AC3">
-        <v>3.9478898578809751</v>
-      </c>
-      <c r="AD3">
-        <v>5351</v>
-      </c>
-      <c r="AE3">
-        <v>8891.49</v>
-      </c>
-      <c r="AF3">
-        <v>310.76</v>
-      </c>
-      <c r="AG3">
-        <v>3101.1</v>
-      </c>
-      <c r="AH3">
-        <v>22.59</v>
-      </c>
-      <c r="AI3">
-        <v>1559.66</v>
-      </c>
-      <c r="AJ3">
-        <v>1.9</v>
-      </c>
-      <c r="AK3">
-        <v>3430.9</v>
-      </c>
-      <c r="AL3">
-        <v>3.4</v>
-      </c>
-      <c r="AM3">
-        <v>4</v>
-      </c>
-      <c r="AN3">
-        <v>1285</v>
-      </c>
-      <c r="AO3">
-        <v>31.5</v>
-      </c>
-      <c r="AP3">
-        <v>6.4</v>
-      </c>
-      <c r="AQ3">
-        <v>55.1</v>
-      </c>
-      <c r="AR3">
-        <v>13.7</v>
-      </c>
-      <c r="AS3">
-        <v>2.99</v>
-      </c>
-      <c r="AT3">
-        <v>7.3</v>
-      </c>
-      <c r="AU3">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="AV3">
-        <v>16.53</v>
-      </c>
-      <c r="AW3">
-        <v>23742</v>
-      </c>
-      <c r="AX3">
-        <v>413</v>
-      </c>
-      <c r="AY3">
-        <v>0.68072142659479962</v>
-      </c>
-      <c r="AZ3">
-        <v>7.9873670095453182</v>
-      </c>
-      <c r="BA3">
-        <v>6.7</v>
-      </c>
-      <c r="BB3">
-        <v>38307</v>
-      </c>
-      <c r="BC3">
-        <v>59.2</v>
-      </c>
-      <c r="BD3">
-        <v>59.3</v>
-      </c>
-      <c r="BE3">
-        <v>20.3</v>
-      </c>
-      <c r="BF3">
-        <v>72.099999999999994</v>
-      </c>
+    <row r="19" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="K19" s="12"/>
     </row>
-    <row r="4" spans="1:58">
-      <c r="A4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B4">
-        <v>2011047</v>
-      </c>
-      <c r="C4">
-        <v>81</v>
-      </c>
-      <c r="D4">
-        <v>46.3</v>
-      </c>
-      <c r="E4">
-        <v>4.51903680676691</v>
-      </c>
-      <c r="F4">
-        <v>9.9</v>
-      </c>
-      <c r="G4">
-        <v>99.509</v>
-      </c>
-      <c r="H4">
-        <v>99.76</v>
-      </c>
-      <c r="I4">
-        <v>933</v>
-      </c>
-      <c r="J4">
-        <v>10.674600022243052</v>
-      </c>
-      <c r="K4">
-        <v>337</v>
-      </c>
-      <c r="L4" s="12"/>
-      <c r="M4">
-        <v>83.1</v>
-      </c>
-      <c r="N4">
-        <v>62534</v>
-      </c>
-      <c r="O4">
-        <v>1084</v>
-      </c>
-      <c r="P4">
-        <v>340.55</v>
-      </c>
-      <c r="Q4">
-        <v>76</v>
-      </c>
-      <c r="R4">
-        <v>7771.05</v>
-      </c>
-      <c r="S4">
-        <v>0.44</v>
-      </c>
-      <c r="T4">
-        <v>521.20000000000005</v>
-      </c>
-      <c r="U4">
-        <v>37073.199999999997</v>
-      </c>
-      <c r="V4">
-        <v>24530.2</v>
-      </c>
-      <c r="W4">
-        <v>13319</v>
-      </c>
-      <c r="X4">
-        <v>1.4</v>
-      </c>
-      <c r="Y4">
-        <v>60.22</v>
-      </c>
-      <c r="Z4">
-        <v>23473</v>
-      </c>
-      <c r="AA4">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="AB4">
-        <v>618.02931507816572</v>
-      </c>
-      <c r="AC4">
-        <v>4.2017914051735241</v>
-      </c>
-      <c r="AD4">
-        <v>3706</v>
-      </c>
-      <c r="AE4">
-        <v>8459.0400000000009</v>
-      </c>
-      <c r="AF4">
-        <v>318.47000000000003</v>
-      </c>
-      <c r="AG4">
-        <v>3193.55</v>
-      </c>
-      <c r="AH4">
-        <v>22.44</v>
-      </c>
-      <c r="AI4">
-        <v>1819.42</v>
-      </c>
-      <c r="AJ4">
-        <v>2.8</v>
-      </c>
-      <c r="AK4">
-        <v>3289.6</v>
-      </c>
-      <c r="AL4">
-        <v>2.9</v>
-      </c>
-      <c r="AM4">
-        <v>2</v>
-      </c>
-      <c r="AN4">
-        <v>1589</v>
-      </c>
-      <c r="AO4">
-        <v>38.9</v>
-      </c>
-      <c r="AP4">
-        <v>10.6</v>
-      </c>
-      <c r="AQ4">
-        <v>68.400000000000006</v>
-      </c>
-      <c r="AR4">
-        <v>16.7</v>
-      </c>
-      <c r="AS4">
-        <v>2.27</v>
-      </c>
-      <c r="AT4">
-        <v>7.4</v>
-      </c>
-      <c r="AU4">
-        <v>3.5</v>
-      </c>
-      <c r="AV4">
-        <v>13.52</v>
-      </c>
-      <c r="AW4">
-        <v>11892</v>
-      </c>
-      <c r="AX4">
-        <v>413</v>
-      </c>
-      <c r="AY4">
-        <v>0.71664539014003525</v>
-      </c>
-      <c r="AZ4">
-        <v>10.927709229464034</v>
-      </c>
-      <c r="BA4">
-        <v>6.8</v>
-      </c>
-      <c r="BB4">
-        <v>19658</v>
-      </c>
-      <c r="BC4">
-        <v>56.7</v>
-      </c>
-      <c r="BD4">
-        <v>58.6</v>
-      </c>
-      <c r="BE4">
-        <v>23.4</v>
-      </c>
-      <c r="BF4">
-        <v>73.599999999999994</v>
-      </c>
+    <row r="20" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="K20" s="12"/>
     </row>
-    <row r="5" spans="1:58">
-      <c r="A5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B5">
-        <v>975023</v>
-      </c>
-      <c r="C5">
-        <v>71</v>
-      </c>
-      <c r="D5">
-        <v>64.599999999999994</v>
-      </c>
-      <c r="E5">
-        <v>4.362735355569388</v>
-      </c>
-      <c r="F5">
-        <v>10.9</v>
-      </c>
-      <c r="G5">
-        <v>99.504999999999995</v>
-      </c>
-      <c r="H5">
-        <v>99.92</v>
-      </c>
-      <c r="I5">
-        <v>955</v>
-      </c>
-      <c r="J5">
-        <v>9.4729169863434084</v>
-      </c>
-      <c r="K5">
-        <v>127</v>
-      </c>
-      <c r="L5" s="12"/>
-      <c r="M5">
-        <v>83.1</v>
-      </c>
-      <c r="N5">
-        <v>72438</v>
-      </c>
-      <c r="O5">
-        <v>1386</v>
-      </c>
-      <c r="P5">
-        <v>472.11</v>
-      </c>
-      <c r="Q5">
-        <v>102</v>
-      </c>
-      <c r="R5">
-        <v>7887.19</v>
-      </c>
-      <c r="S5">
-        <v>0.42</v>
-      </c>
-      <c r="T5">
-        <v>656.9</v>
-      </c>
-      <c r="U5">
-        <v>14896.1</v>
-      </c>
-      <c r="V5">
-        <v>8909.2999999999993</v>
-      </c>
-      <c r="W5">
-        <v>3811</v>
-      </c>
-      <c r="X5">
-        <v>1.9</v>
-      </c>
-      <c r="Y5">
-        <v>45.36</v>
-      </c>
-      <c r="Z5">
-        <v>15175</v>
-      </c>
-      <c r="AA5">
-        <v>6.5</v>
-      </c>
-      <c r="AB5">
-        <v>663.50024563523118</v>
-      </c>
-      <c r="AC5">
-        <v>4.7383497620056145</v>
-      </c>
-      <c r="AD5">
-        <v>6013</v>
-      </c>
-      <c r="AE5">
-        <v>8923.2000000000007</v>
-      </c>
-      <c r="AF5">
-        <v>330.59</v>
-      </c>
-      <c r="AG5">
-        <v>3110.36</v>
-      </c>
-      <c r="AH5">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="AI5">
-        <v>1753.55</v>
-      </c>
-      <c r="AJ5">
-        <v>2.4</v>
-      </c>
-      <c r="AK5">
-        <v>3923</v>
-      </c>
-      <c r="AL5">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="AM5">
-        <v>3</v>
-      </c>
-      <c r="AN5">
-        <v>2470</v>
-      </c>
-      <c r="AO5">
-        <v>25</v>
-      </c>
-      <c r="AP5">
-        <v>7.9</v>
-      </c>
-      <c r="AQ5">
-        <v>47</v>
-      </c>
-      <c r="AR5">
-        <v>10.7</v>
-      </c>
-      <c r="AS5">
-        <v>1.39</v>
-      </c>
-      <c r="AT5">
-        <v>4.5</v>
-      </c>
-      <c r="AU5">
-        <v>3.4</v>
-      </c>
-      <c r="AV5">
-        <v>18.440000000000001</v>
-      </c>
-      <c r="AW5">
-        <v>15088</v>
-      </c>
-      <c r="AX5">
-        <v>425</v>
-      </c>
-      <c r="AY5">
-        <v>0.78358536459872896</v>
-      </c>
-      <c r="AZ5">
-        <v>12.764234226937718</v>
-      </c>
-      <c r="BA5">
-        <v>9</v>
-      </c>
-      <c r="BB5">
-        <v>22775</v>
-      </c>
-      <c r="BC5">
-        <v>56.6</v>
-      </c>
-      <c r="BD5">
-        <v>59</v>
-      </c>
-      <c r="BE5">
-        <v>20</v>
-      </c>
-      <c r="BF5">
-        <v>72.3</v>
-      </c>
+    <row r="21" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="K21" s="12"/>
     </row>
-    <row r="6" spans="1:58">
-      <c r="A6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B6">
-        <v>2362519</v>
-      </c>
-      <c r="C6">
-        <v>132</v>
-      </c>
-      <c r="D6">
-        <v>62.1</v>
-      </c>
-      <c r="E6">
-        <v>2.5842161469634721</v>
-      </c>
-      <c r="F6">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="G6">
-        <v>99.355000000000004</v>
-      </c>
-      <c r="H6">
-        <v>99.94</v>
-      </c>
-      <c r="I6">
-        <v>961</v>
-      </c>
-      <c r="J6">
-        <v>11.298931508198336</v>
-      </c>
-      <c r="K6">
-        <v>293</v>
-      </c>
-      <c r="L6" s="12"/>
-      <c r="M6">
-        <v>83.4</v>
-      </c>
-      <c r="N6">
-        <v>86151</v>
-      </c>
-      <c r="O6">
-        <v>1236</v>
-      </c>
-      <c r="P6">
-        <v>487.43</v>
-      </c>
-      <c r="Q6">
-        <v>85</v>
-      </c>
-      <c r="R6">
-        <v>8096.32</v>
-      </c>
-      <c r="S6">
-        <v>0.96</v>
-      </c>
-      <c r="T6">
-        <v>699.5</v>
-      </c>
-      <c r="U6">
-        <v>25482.799999999999</v>
-      </c>
-      <c r="V6">
-        <v>21494.799999999999</v>
-      </c>
-      <c r="W6">
-        <v>13240</v>
-      </c>
-      <c r="X6">
-        <v>1.5</v>
-      </c>
-      <c r="Y6">
-        <v>86.44</v>
-      </c>
-      <c r="Z6">
-        <v>28532</v>
-      </c>
-      <c r="AA6">
-        <v>6</v>
-      </c>
-      <c r="AB6">
-        <v>619.10443894842751</v>
-      </c>
-      <c r="AC6">
-        <v>9.4560086077614613</v>
-      </c>
-      <c r="AD6">
-        <v>5286</v>
-      </c>
-      <c r="AE6">
-        <v>9046.44</v>
-      </c>
-      <c r="AF6">
-        <v>319.74</v>
-      </c>
-      <c r="AG6">
-        <v>2940.9</v>
-      </c>
-      <c r="AH6">
-        <v>20.72</v>
-      </c>
-      <c r="AI6">
-        <v>1754.42</v>
-      </c>
-      <c r="AJ6">
-        <v>1.9</v>
-      </c>
-      <c r="AK6">
-        <v>3312.6</v>
-      </c>
-      <c r="AL6">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="AM6">
-        <v>3</v>
-      </c>
-      <c r="AN6">
-        <v>1027</v>
-      </c>
-      <c r="AO6">
-        <v>43.1</v>
-      </c>
-      <c r="AP6">
-        <v>11.6</v>
-      </c>
-      <c r="AQ6">
-        <v>55.5</v>
-      </c>
-      <c r="AR6">
-        <v>16.7</v>
-      </c>
-      <c r="AS6">
-        <v>2.7</v>
-      </c>
-      <c r="AT6">
-        <v>5.4</v>
-      </c>
-      <c r="AU6">
-        <v>3.1</v>
-      </c>
-      <c r="AV6">
-        <v>9.9499999999999993</v>
-      </c>
-      <c r="AW6">
-        <v>10905</v>
-      </c>
-      <c r="AX6">
-        <v>461</v>
-      </c>
-      <c r="AY6">
-        <v>0.85471184747370232</v>
-      </c>
-      <c r="AZ6">
-        <v>10.775555265031013</v>
-      </c>
-      <c r="BA6">
-        <v>7.8</v>
-      </c>
-      <c r="BB6">
-        <v>68281</v>
-      </c>
-      <c r="BC6">
-        <v>56.1</v>
-      </c>
-      <c r="BD6">
-        <v>57.9</v>
-      </c>
-      <c r="BE6">
-        <v>23</v>
-      </c>
-      <c r="BF6">
-        <v>76</v>
-      </c>
+    <row r="22" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="K22" s="12"/>
+      <c r="X22" s="14"/>
     </row>
-    <row r="7" spans="1:58">
-      <c r="A7" t="s">
-        <v>130</v>
-      </c>
-      <c r="B7">
-        <v>3429632</v>
-      </c>
-      <c r="C7">
-        <v>226</v>
-      </c>
-      <c r="D7">
-        <v>48</v>
-      </c>
-      <c r="E7">
-        <v>4.1760396469417689</v>
-      </c>
-      <c r="F7">
-        <v>10.7</v>
-      </c>
-      <c r="G7">
-        <v>99.817999999999998</v>
-      </c>
-      <c r="H7">
-        <v>100.17</v>
-      </c>
-      <c r="I7">
-        <v>954</v>
-      </c>
-      <c r="J7">
-        <v>11.915542441710141</v>
-      </c>
-      <c r="K7">
-        <v>457</v>
-      </c>
-      <c r="L7" s="12"/>
-      <c r="M7">
-        <v>87</v>
-      </c>
-      <c r="N7">
-        <v>80976</v>
-      </c>
-      <c r="O7">
-        <v>1456</v>
-      </c>
-      <c r="P7">
-        <v>540.98</v>
-      </c>
-      <c r="Q7">
-        <v>109</v>
-      </c>
-      <c r="R7">
-        <v>8818.7099999999991</v>
-      </c>
-      <c r="S7">
-        <v>0.39</v>
-      </c>
-      <c r="T7">
-        <v>892.7</v>
-      </c>
-      <c r="U7">
-        <v>31838.9</v>
-      </c>
-      <c r="V7">
-        <v>26456.6</v>
-      </c>
-      <c r="W7">
-        <v>17635</v>
-      </c>
-      <c r="X7">
-        <v>1.7</v>
-      </c>
-      <c r="Y7">
-        <v>118.01</v>
-      </c>
-      <c r="Z7">
-        <v>8848</v>
-      </c>
-      <c r="AA7">
-        <v>7.1</v>
-      </c>
-      <c r="AB7">
-        <v>569.33047044114346</v>
-      </c>
-      <c r="AC7">
-        <v>7.2136019258042845</v>
-      </c>
-      <c r="AD7">
-        <v>4945</v>
-      </c>
-      <c r="AE7">
-        <v>8723.18</v>
-      </c>
-      <c r="AF7">
-        <v>346.86</v>
-      </c>
-      <c r="AG7">
-        <v>3323.19</v>
-      </c>
-      <c r="AH7">
-        <v>32.51</v>
-      </c>
-      <c r="AI7">
-        <v>1425.3</v>
-      </c>
-      <c r="AJ7">
-        <v>2.1</v>
-      </c>
-      <c r="AK7">
-        <v>3337.4</v>
-      </c>
-      <c r="AL7">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="AM7">
-        <v>7</v>
-      </c>
-      <c r="AN7">
-        <v>2081</v>
-      </c>
-      <c r="AO7">
-        <v>37.1</v>
-      </c>
-      <c r="AP7">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="AQ7">
-        <v>57.1</v>
-      </c>
-      <c r="AR7">
-        <v>14.8</v>
-      </c>
-      <c r="AS7">
-        <v>2.16</v>
-      </c>
-      <c r="AT7">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="AU7">
-        <v>2.7</v>
-      </c>
-      <c r="AV7">
-        <v>30.18</v>
-      </c>
-      <c r="AW7">
-        <v>45212</v>
-      </c>
-      <c r="AX7">
-        <v>398</v>
-      </c>
-      <c r="AY7">
-        <v>0.94971440391924344</v>
-      </c>
-      <c r="AZ7">
-        <v>11.593814419830618</v>
-      </c>
-      <c r="BA7">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="BB7">
-        <v>30064</v>
-      </c>
-      <c r="BC7">
-        <v>59.3</v>
-      </c>
-      <c r="BD7">
-        <v>60.2</v>
-      </c>
-      <c r="BE7">
-        <v>25.6</v>
-      </c>
-      <c r="BF7">
-        <v>68.900000000000006</v>
-      </c>
+    <row r="23" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="I23" s="14"/>
+      <c r="K23" s="12"/>
+      <c r="X23" s="14"/>
     </row>
-    <row r="8" spans="1:58">
-      <c r="A8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B8">
-        <v>5510527</v>
-      </c>
-      <c r="C8">
-        <v>155</v>
-      </c>
-      <c r="D8">
-        <v>64.7</v>
-      </c>
-      <c r="E8">
-        <v>2.2331409202932018</v>
-      </c>
-      <c r="F8">
-        <v>13.2</v>
-      </c>
-      <c r="G8">
-        <v>99.721999999999994</v>
-      </c>
-      <c r="H8">
-        <v>100.25</v>
-      </c>
-      <c r="I8">
-        <v>982</v>
-      </c>
-      <c r="J8">
-        <v>15.608251387133988</v>
-      </c>
-      <c r="K8">
-        <v>516</v>
-      </c>
-      <c r="L8" s="12"/>
-      <c r="M8">
-        <v>85.5</v>
-      </c>
-      <c r="N8">
-        <v>142761</v>
-      </c>
-      <c r="O8">
-        <v>1911</v>
-      </c>
-      <c r="P8">
-        <v>1077.07</v>
-      </c>
-      <c r="Q8">
-        <v>144</v>
-      </c>
-      <c r="R8">
-        <v>10018.709999999999</v>
-      </c>
-      <c r="S8">
-        <v>0.81</v>
-      </c>
-      <c r="T8">
-        <v>903</v>
-      </c>
-      <c r="U8">
-        <v>56326.3</v>
-      </c>
-      <c r="V8">
-        <v>41864.800000000003</v>
-      </c>
-      <c r="W8">
-        <v>24985</v>
-      </c>
-      <c r="X8">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="Y8">
-        <v>153.68</v>
-      </c>
-      <c r="Z8">
-        <v>70180</v>
-      </c>
-      <c r="AA8">
-        <v>5</v>
-      </c>
-      <c r="AB8">
-        <v>673.88708920217607</v>
-      </c>
-      <c r="AC8">
-        <v>5.2009544640648713</v>
-      </c>
-      <c r="AD8">
-        <v>13687</v>
-      </c>
-      <c r="AE8">
-        <v>10843.21</v>
-      </c>
-      <c r="AF8">
-        <v>393.91</v>
-      </c>
-      <c r="AG8">
-        <v>3819.62</v>
-      </c>
-      <c r="AH8">
-        <v>18.489999999999998</v>
-      </c>
-      <c r="AI8">
-        <v>1713.91</v>
-      </c>
-      <c r="AJ8">
-        <v>1.7</v>
-      </c>
-      <c r="AK8">
-        <v>3191.5</v>
-      </c>
-      <c r="AL8">
-        <v>5.7</v>
-      </c>
-      <c r="AM8">
-        <v>7</v>
-      </c>
-      <c r="AN8">
-        <v>1680</v>
-      </c>
-      <c r="AO8">
-        <v>52.2</v>
-      </c>
-      <c r="AP8">
-        <v>12.2</v>
-      </c>
-      <c r="AQ8">
-        <v>63.6</v>
-      </c>
-      <c r="AR8">
-        <v>16.3</v>
-      </c>
-      <c r="AS8">
-        <v>2.79</v>
-      </c>
-      <c r="AT8">
-        <v>4</v>
-      </c>
-      <c r="AU8">
-        <v>2.5</v>
-      </c>
-      <c r="AV8">
-        <v>13.09</v>
-      </c>
-      <c r="AW8">
-        <v>20224</v>
-      </c>
-      <c r="AX8">
-        <v>464.8</v>
-      </c>
-      <c r="AY8">
-        <v>0.95622626003703926</v>
-      </c>
-      <c r="AZ8">
-        <v>5.8247130583527209</v>
-      </c>
-      <c r="BA8">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="BB8">
-        <v>120290</v>
-      </c>
-      <c r="BC8">
-        <v>63.3</v>
-      </c>
-      <c r="BD8">
-        <v>59.1</v>
-      </c>
-      <c r="BE8">
-        <v>32.4</v>
-      </c>
-      <c r="BF8">
-        <v>70.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:58">
-      <c r="A9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B9">
-        <v>936725</v>
-      </c>
-      <c r="C9">
-        <v>101</v>
-      </c>
-      <c r="D9">
-        <v>53.2</v>
-      </c>
-      <c r="E9">
-        <v>5.7863002327767719</v>
-      </c>
-      <c r="F9">
-        <v>9.9</v>
-      </c>
-      <c r="G9">
-        <v>99.427000000000007</v>
-      </c>
-      <c r="H9">
-        <v>99.88</v>
-      </c>
-      <c r="I9">
-        <v>980</v>
-      </c>
-      <c r="J9">
-        <v>13.967230034834214</v>
-      </c>
-      <c r="K9">
-        <v>233</v>
-      </c>
-      <c r="L9" s="12"/>
-      <c r="M9">
-        <v>81</v>
-      </c>
-      <c r="N9">
-        <v>72963</v>
-      </c>
-      <c r="O9">
-        <v>1232</v>
-      </c>
-      <c r="P9">
-        <v>469.91</v>
-      </c>
-      <c r="Q9">
-        <v>71</v>
-      </c>
-      <c r="R9">
-        <v>7958.35</v>
-      </c>
-      <c r="S9">
-        <v>0.08</v>
-      </c>
-      <c r="T9">
-        <v>730.1</v>
-      </c>
-      <c r="U9">
-        <v>10409.5</v>
-      </c>
-      <c r="V9">
-        <v>8636</v>
-      </c>
-      <c r="W9">
-        <v>4786</v>
-      </c>
-      <c r="X9">
-        <v>0.9</v>
-      </c>
-      <c r="Y9">
-        <v>29.91</v>
-      </c>
-      <c r="Z9">
-        <v>13845</v>
-      </c>
-      <c r="AA9">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="AB9">
-        <v>621.51538605247003</v>
-      </c>
-      <c r="AC9">
-        <v>5.2736929194801032</v>
-      </c>
-      <c r="AD9">
-        <v>7197</v>
-      </c>
-      <c r="AE9">
-        <v>8618.2900000000009</v>
-      </c>
-      <c r="AF9">
-        <v>337.92</v>
-      </c>
-      <c r="AG9">
-        <v>3039.54</v>
-      </c>
-      <c r="AH9">
-        <v>14.94</v>
-      </c>
-      <c r="AI9">
-        <v>1417.39</v>
-      </c>
-      <c r="AJ9">
-        <v>3.2</v>
-      </c>
-      <c r="AK9">
-        <v>3935</v>
-      </c>
-      <c r="AL9">
-        <v>5</v>
-      </c>
-      <c r="AM9">
-        <v>3</v>
-      </c>
-      <c r="AN9">
-        <v>958</v>
-      </c>
-      <c r="AO9">
-        <v>25.7</v>
-      </c>
-      <c r="AP9">
-        <v>7.2</v>
-      </c>
-      <c r="AQ9">
-        <v>55.4</v>
-      </c>
-      <c r="AR9">
-        <v>12.9</v>
-      </c>
-      <c r="AS9">
-        <v>2.72</v>
-      </c>
-      <c r="AT9">
-        <v>5.9</v>
-      </c>
-      <c r="AU9">
-        <v>2.9</v>
-      </c>
-      <c r="AV9">
-        <v>8.4600000000000009</v>
-      </c>
-      <c r="AW9">
-        <v>8273</v>
-      </c>
-      <c r="AX9">
-        <v>398</v>
-      </c>
-      <c r="AY9">
-        <v>1.0219749238313738</v>
-      </c>
-      <c r="AZ9">
-        <v>11.911139848512839</v>
-      </c>
-      <c r="BA9">
-        <v>10.6</v>
-      </c>
-      <c r="BB9">
-        <v>19570</v>
-      </c>
-      <c r="BC9">
-        <v>59.5</v>
-      </c>
-      <c r="BD9">
-        <v>60.3</v>
-      </c>
-      <c r="BE9">
-        <v>20.7</v>
-      </c>
-      <c r="BF9">
-        <v>70.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:58">
-      <c r="A10" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10">
-        <v>2071676</v>
-      </c>
-      <c r="C10">
-        <v>117</v>
-      </c>
-      <c r="D10">
-        <v>41.3</v>
-      </c>
-      <c r="E10">
-        <v>6.4209691596285392</v>
-      </c>
-      <c r="F10">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="G10">
-        <v>99.688000000000002</v>
-      </c>
-      <c r="H10">
-        <v>99.88</v>
-      </c>
-      <c r="I10">
-        <v>940</v>
-      </c>
-      <c r="J10">
-        <v>14.720645161290323</v>
-      </c>
-      <c r="K10">
-        <v>221</v>
-      </c>
-      <c r="L10" s="12"/>
-      <c r="M10">
-        <v>84.1</v>
-      </c>
-      <c r="N10">
-        <v>64987</v>
-      </c>
-      <c r="O10">
-        <v>1038</v>
-      </c>
-      <c r="P10">
-        <v>473.35</v>
-      </c>
-      <c r="Q10">
-        <v>73</v>
-      </c>
-      <c r="R10">
-        <v>7514.69</v>
-      </c>
-      <c r="S10">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="T10">
-        <v>491</v>
-      </c>
-      <c r="U10">
-        <v>20577.7</v>
-      </c>
-      <c r="V10">
-        <v>17143.099999999999</v>
-      </c>
-      <c r="W10">
-        <v>11007</v>
-      </c>
-      <c r="X10">
-        <v>1.5</v>
-      </c>
-      <c r="Y10">
-        <v>22.51</v>
-      </c>
-      <c r="Z10">
-        <v>29325</v>
-      </c>
-      <c r="AA10">
-        <v>5.5</v>
-      </c>
-      <c r="AB10">
-        <v>575.42492165763372</v>
-      </c>
-      <c r="AC10">
-        <v>4.8994147733525901</v>
-      </c>
-      <c r="AD10">
-        <v>4557</v>
-      </c>
-      <c r="AE10">
-        <v>8554.35</v>
-      </c>
-      <c r="AF10">
-        <v>307.3</v>
-      </c>
-      <c r="AG10">
-        <v>3121.56</v>
-      </c>
-      <c r="AH10">
-        <v>19.25</v>
-      </c>
-      <c r="AI10">
-        <v>1885.43</v>
-      </c>
-      <c r="AJ10">
-        <v>3.2</v>
-      </c>
-      <c r="AK10">
-        <v>4132.2</v>
-      </c>
-      <c r="AL10">
-        <v>3.8</v>
-      </c>
-      <c r="AM10">
-        <v>4</v>
-      </c>
-      <c r="AN10">
-        <v>1576</v>
-      </c>
-      <c r="AO10">
-        <v>28.6</v>
-      </c>
-      <c r="AP10">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="AQ10">
-        <v>65</v>
-      </c>
-      <c r="AR10">
-        <v>16.8</v>
-      </c>
-      <c r="AS10">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="AT10">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="AU10">
-        <v>4</v>
-      </c>
-      <c r="AV10">
-        <v>16.739999999999998</v>
-      </c>
-      <c r="AW10">
-        <v>17270</v>
-      </c>
-      <c r="AX10">
-        <v>353</v>
-      </c>
-      <c r="AY10">
-        <v>0.62717353919058361</v>
-      </c>
-      <c r="AZ10">
-        <v>9.1466888723320334</v>
-      </c>
-      <c r="BA10">
-        <v>7.2</v>
-      </c>
-      <c r="BB10">
-        <v>13762</v>
-      </c>
-      <c r="BC10">
-        <v>52.7</v>
-      </c>
-      <c r="BD10">
-        <v>60.1</v>
-      </c>
-      <c r="BE10">
-        <v>22.2</v>
-      </c>
-      <c r="BF10">
-        <v>69.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:58">
-      <c r="A11" t="s">
-        <v>134</v>
-      </c>
-      <c r="B11">
-        <v>1138216</v>
-      </c>
-      <c r="C11">
-        <v>57</v>
-      </c>
-      <c r="D11">
-        <v>60.9</v>
-      </c>
-      <c r="E11">
-        <v>5.9628358036980531</v>
-      </c>
-      <c r="F11">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G11">
-        <v>99.608000000000004</v>
-      </c>
-      <c r="H11">
-        <v>99.89</v>
-      </c>
-      <c r="I11">
-        <v>946</v>
-      </c>
-      <c r="J11">
-        <v>11.094423012097831</v>
-      </c>
-      <c r="K11">
-        <v>262</v>
-      </c>
-      <c r="L11" s="12"/>
-      <c r="M11">
-        <v>82.4</v>
-      </c>
-      <c r="N11">
-        <v>70079</v>
-      </c>
-      <c r="O11">
-        <v>1093</v>
-      </c>
-      <c r="P11">
-        <v>397.31</v>
-      </c>
-      <c r="Q11">
-        <v>76</v>
-      </c>
-      <c r="R11">
-        <v>7850.16</v>
-      </c>
-      <c r="S11">
-        <v>0.82</v>
-      </c>
-      <c r="T11">
-        <v>456</v>
-      </c>
-      <c r="U11">
-        <v>27367.3</v>
-      </c>
-      <c r="V11">
-        <v>15371.2</v>
-      </c>
-      <c r="W11">
-        <v>7384</v>
-      </c>
-      <c r="X11">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="Y11">
-        <v>56.6</v>
-      </c>
-      <c r="Z11">
-        <v>30355</v>
-      </c>
-      <c r="AA11">
-        <v>3.8</v>
-      </c>
-      <c r="AB11">
-        <v>547.56390702643432</v>
-      </c>
-      <c r="AC11">
-        <v>3.0486304884134472</v>
-      </c>
-      <c r="AD11">
-        <v>3702</v>
-      </c>
-      <c r="AE11">
-        <v>9329.51</v>
-      </c>
-      <c r="AF11">
-        <v>336.86</v>
-      </c>
-      <c r="AG11">
-        <v>3355.05</v>
-      </c>
-      <c r="AH11">
-        <v>22.95</v>
-      </c>
-      <c r="AI11">
-        <v>2219.9899999999998</v>
-      </c>
-      <c r="AJ11">
-        <v>2</v>
-      </c>
-      <c r="AK11">
-        <v>4311.1000000000004</v>
-      </c>
-      <c r="AL11">
-        <v>3.7</v>
-      </c>
-      <c r="AM11">
-        <v>4</v>
-      </c>
-      <c r="AN11">
-        <v>1557</v>
-      </c>
-      <c r="AO11">
-        <v>41.4</v>
-      </c>
-      <c r="AP11">
-        <v>11.1</v>
-      </c>
-      <c r="AQ11">
-        <v>63.2</v>
-      </c>
-      <c r="AR11">
-        <v>16.8</v>
-      </c>
-      <c r="AS11">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="AT11">
-        <v>7</v>
-      </c>
-      <c r="AU11">
-        <v>4.3</v>
-      </c>
-      <c r="AV11">
-        <v>12.73</v>
-      </c>
-      <c r="AW11">
-        <v>11274</v>
-      </c>
-      <c r="AX11">
-        <v>425</v>
-      </c>
-      <c r="AY11">
-        <v>0.61943214965480731</v>
-      </c>
-      <c r="AZ11">
-        <v>11.866581141757537</v>
-      </c>
-      <c r="BA11">
-        <v>6.1</v>
-      </c>
-      <c r="BB11">
-        <v>13009</v>
-      </c>
-      <c r="BC11">
-        <v>56.1</v>
-      </c>
-      <c r="BD11">
-        <v>59.6</v>
-      </c>
-      <c r="BE11">
-        <v>23.8</v>
-      </c>
-      <c r="BF11">
-        <v>72.099999999999994</v>
-      </c>
-    </row>
-    <row r="12" spans="1:58">
-      <c r="A12" t="s">
-        <v>135</v>
-      </c>
-      <c r="B12">
-        <v>2359573</v>
-      </c>
-      <c r="C12">
-        <v>129</v>
-      </c>
-      <c r="D12">
-        <v>63.1</v>
-      </c>
-      <c r="E12">
-        <v>3.7803522644358849</v>
-      </c>
-      <c r="F12">
-        <v>13.8</v>
-      </c>
-      <c r="G12">
-        <v>99.753</v>
-      </c>
-      <c r="H12">
-        <v>100.23</v>
-      </c>
-      <c r="I12">
-        <v>921</v>
-      </c>
-      <c r="J12">
-        <v>15.089281462787486</v>
-      </c>
-      <c r="K12">
-        <v>403</v>
-      </c>
-      <c r="L12" s="12"/>
-      <c r="M12">
-        <v>83.1</v>
-      </c>
-      <c r="N12">
-        <v>86643</v>
-      </c>
-      <c r="O12">
-        <v>1567</v>
-      </c>
-      <c r="P12">
-        <v>601.32000000000005</v>
-      </c>
-      <c r="Q12">
-        <v>121</v>
-      </c>
-      <c r="R12">
-        <v>8620.2800000000007</v>
-      </c>
-      <c r="S12">
-        <v>1.79</v>
-      </c>
-      <c r="T12">
-        <v>930.4</v>
-      </c>
-      <c r="U12">
-        <v>20982.9</v>
-      </c>
-      <c r="V12">
-        <v>15472.4</v>
-      </c>
-      <c r="W12">
-        <v>10821</v>
-      </c>
-      <c r="X12">
-        <v>1.4</v>
-      </c>
-      <c r="Y12">
-        <v>124.78</v>
-      </c>
-      <c r="Z12">
-        <v>29162</v>
-      </c>
-      <c r="AA12">
-        <v>6.4</v>
-      </c>
-      <c r="AB12">
-        <v>583.79461029601543</v>
-      </c>
-      <c r="AC12">
-        <v>7.1453606224516042</v>
-      </c>
-      <c r="AD12">
-        <v>7456</v>
-      </c>
-      <c r="AE12">
-        <v>9257.75</v>
-      </c>
-      <c r="AF12">
-        <v>299.87</v>
-      </c>
-      <c r="AG12">
-        <v>3362.2</v>
-      </c>
-      <c r="AH12">
-        <v>10.86</v>
-      </c>
-      <c r="AI12">
-        <v>1400.22</v>
-      </c>
-      <c r="AJ12">
-        <v>1.3</v>
-      </c>
-      <c r="AK12">
-        <v>2087.9</v>
-      </c>
-      <c r="AL12">
-        <v>5.4</v>
-      </c>
-      <c r="AM12">
-        <v>4</v>
-      </c>
-      <c r="AN12">
-        <v>1583</v>
-      </c>
-      <c r="AO12">
-        <v>36.799999999999997</v>
-      </c>
-      <c r="AP12">
-        <v>10.1</v>
-      </c>
-      <c r="AQ12">
-        <v>45.8</v>
-      </c>
-      <c r="AR12">
-        <v>12</v>
-      </c>
-      <c r="AS12">
-        <v>1.74</v>
-      </c>
-      <c r="AT12">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="AU12">
-        <v>3.3</v>
-      </c>
-      <c r="AV12">
-        <v>49.07</v>
-      </c>
-      <c r="AW12">
-        <v>46251</v>
-      </c>
-      <c r="AX12">
-        <v>425</v>
-      </c>
-      <c r="AY12">
-        <v>0.87357677362428521</v>
-      </c>
-      <c r="AZ12">
-        <v>8.275216426309866</v>
-      </c>
-      <c r="BA12">
-        <v>6.3</v>
-      </c>
-      <c r="BB12">
-        <v>46931</v>
-      </c>
-      <c r="BC12">
-        <v>60.1</v>
-      </c>
-      <c r="BD12">
-        <v>59.6</v>
-      </c>
-      <c r="BE12">
-        <v>25.4</v>
-      </c>
-      <c r="BF12">
-        <v>70.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:58">
-      <c r="A13" t="s">
-        <v>136</v>
-      </c>
-      <c r="B13">
-        <v>4320130</v>
-      </c>
-      <c r="C13">
-        <v>355</v>
-      </c>
-      <c r="D13">
-        <v>76.099999999999994</v>
-      </c>
-      <c r="E13">
-        <v>3.1418935032194324</v>
-      </c>
-      <c r="F13">
-        <v>9.6</v>
-      </c>
-      <c r="G13">
-        <v>99.394999999999996</v>
-      </c>
-      <c r="H13">
-        <v>99.93</v>
-      </c>
-      <c r="I13">
-        <v>974</v>
-      </c>
-      <c r="J13">
-        <v>14.224033639107812</v>
-      </c>
-      <c r="K13">
-        <v>282</v>
-      </c>
-      <c r="L13" s="12"/>
-      <c r="M13">
-        <v>84.3</v>
-      </c>
-      <c r="N13">
-        <v>93591</v>
-      </c>
-      <c r="O13">
-        <v>1271</v>
-      </c>
-      <c r="P13">
-        <v>540.98</v>
-      </c>
-      <c r="Q13">
-        <v>82</v>
-      </c>
-      <c r="R13">
-        <v>8537.5400000000009</v>
-      </c>
-      <c r="S13">
-        <v>1.76</v>
-      </c>
-      <c r="T13">
-        <v>1323.2</v>
-      </c>
-      <c r="U13">
-        <v>24539.599999999999</v>
-      </c>
-      <c r="V13">
-        <v>21838.5</v>
-      </c>
-      <c r="W13">
-        <v>15037</v>
-      </c>
-      <c r="X13">
-        <v>3.2</v>
-      </c>
-      <c r="Y13">
-        <v>79.680000000000007</v>
-      </c>
-      <c r="Z13">
-        <v>9105</v>
-      </c>
-      <c r="AA13">
-        <v>15.3</v>
-      </c>
-      <c r="AB13">
-        <v>583.70118491804647</v>
-      </c>
-      <c r="AC13">
-        <v>4.134134852423422</v>
-      </c>
-      <c r="AD13">
-        <v>7615</v>
-      </c>
-      <c r="AE13">
-        <v>8987.23</v>
-      </c>
-      <c r="AF13">
-        <v>270.11</v>
-      </c>
-      <c r="AG13">
-        <v>3402.3</v>
-      </c>
-      <c r="AH13">
-        <v>24.06</v>
-      </c>
-      <c r="AI13">
-        <v>1279.55</v>
-      </c>
-      <c r="AJ13">
-        <v>1.7</v>
-      </c>
-      <c r="AK13">
-        <v>3478.7</v>
-      </c>
-      <c r="AL13">
-        <v>5.5</v>
-      </c>
-      <c r="AM13">
-        <v>4</v>
-      </c>
-      <c r="AN13">
-        <v>1531</v>
-      </c>
-      <c r="AO13">
-        <v>38.299999999999997</v>
-      </c>
-      <c r="AP13">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="AQ13">
-        <v>60.9</v>
-      </c>
-      <c r="AR13">
-        <v>14.2</v>
-      </c>
-      <c r="AS13">
-        <v>2.46</v>
-      </c>
-      <c r="AT13">
-        <v>3.6</v>
-      </c>
-      <c r="AU13">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="AV13">
-        <v>11.24</v>
-      </c>
-      <c r="AW13">
-        <v>14305</v>
-      </c>
-      <c r="AX13">
-        <v>445</v>
-      </c>
-      <c r="AY13">
-        <v>0.72480950271976741</v>
-      </c>
-      <c r="AZ13">
-        <v>7.7364535680665885</v>
-      </c>
-      <c r="BA13">
-        <v>6</v>
-      </c>
-      <c r="BB13">
-        <v>147216</v>
-      </c>
-      <c r="BC13">
-        <v>55.9</v>
-      </c>
-      <c r="BD13">
-        <v>58.9</v>
-      </c>
-      <c r="BE13">
-        <v>22.8</v>
-      </c>
-      <c r="BF13">
-        <v>73.599999999999994</v>
-      </c>
-    </row>
-    <row r="14" spans="1:58">
-      <c r="A14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B14">
-        <v>1168499</v>
-      </c>
-      <c r="C14">
-        <v>101</v>
-      </c>
-      <c r="D14">
-        <v>45</v>
-      </c>
-      <c r="E14">
-        <v>4.5242307721236852</v>
-      </c>
-      <c r="F14">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="G14">
-        <v>99.331000000000003</v>
-      </c>
-      <c r="H14">
-        <v>99.77</v>
-      </c>
-      <c r="I14">
-        <v>934</v>
-      </c>
-      <c r="J14">
-        <v>12.972480777013356</v>
-      </c>
-      <c r="K14">
-        <v>166</v>
-      </c>
-      <c r="L14" s="12"/>
-      <c r="M14">
-        <v>85.8</v>
-      </c>
-      <c r="N14">
-        <v>67847</v>
-      </c>
-      <c r="O14">
-        <v>1140</v>
-      </c>
-      <c r="P14">
-        <v>389.77</v>
-      </c>
-      <c r="Q14">
-        <v>76</v>
-      </c>
-      <c r="R14">
-        <v>7664.18</v>
-      </c>
-      <c r="S14">
-        <v>0.48</v>
-      </c>
-      <c r="T14">
-        <v>460.2</v>
-      </c>
-      <c r="U14">
-        <v>17203.599999999999</v>
-      </c>
-      <c r="V14">
-        <v>14862.3</v>
-      </c>
-      <c r="W14">
-        <v>14048</v>
-      </c>
-      <c r="X14">
-        <v>1.3</v>
-      </c>
-      <c r="Y14">
-        <v>41.18</v>
-      </c>
-      <c r="Z14">
-        <v>15454</v>
-      </c>
-      <c r="AA14">
-        <v>6.2</v>
-      </c>
-      <c r="AB14">
-        <v>573.50241634781025</v>
-      </c>
-      <c r="AC14">
-        <v>5.6910617809685755</v>
-      </c>
-      <c r="AD14">
-        <v>3908</v>
-      </c>
-      <c r="AE14">
-        <v>8239.69</v>
-      </c>
-      <c r="AF14">
-        <v>310.55</v>
-      </c>
-      <c r="AG14">
-        <v>2768.03</v>
-      </c>
-      <c r="AH14">
-        <v>22.42</v>
-      </c>
-      <c r="AI14">
-        <v>1567.54</v>
-      </c>
-      <c r="AJ14">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="AK14">
-        <v>3657</v>
-      </c>
-      <c r="AL14">
-        <v>3.2</v>
-      </c>
-      <c r="AM14">
-        <v>3</v>
-      </c>
-      <c r="AN14">
-        <v>1461</v>
-      </c>
-      <c r="AO14">
-        <v>32.200000000000003</v>
-      </c>
-      <c r="AP14">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="AQ14">
-        <v>70.2</v>
-      </c>
-      <c r="AR14">
-        <v>16</v>
-      </c>
-      <c r="AS14">
-        <v>2.36</v>
-      </c>
-      <c r="AT14">
-        <v>7.6</v>
-      </c>
-      <c r="AU14">
-        <v>4.3</v>
-      </c>
-      <c r="AV14">
-        <v>16.579999999999998</v>
-      </c>
-      <c r="AW14">
-        <v>17580</v>
-      </c>
-      <c r="AX14">
-        <v>398</v>
-      </c>
-      <c r="AY14">
-        <v>0.76828767873156067</v>
-      </c>
-      <c r="AZ14">
-        <v>11.4646700982686</v>
-      </c>
-      <c r="BA14">
-        <v>6.2</v>
-      </c>
-      <c r="BB14">
-        <v>10559</v>
-      </c>
-      <c r="BC14">
-        <v>55.5</v>
-      </c>
-      <c r="BD14">
-        <v>58.3</v>
-      </c>
-      <c r="BE14">
-        <v>22.8</v>
-      </c>
-      <c r="BF14">
-        <v>75.599999999999994</v>
-      </c>
-    </row>
-    <row r="15" spans="1:58">
-      <c r="A15" t="s">
-        <v>138</v>
-      </c>
-      <c r="B15">
-        <v>1357910</v>
-      </c>
-      <c r="C15">
-        <v>57</v>
-      </c>
-      <c r="D15">
-        <v>59.3</v>
-      </c>
-      <c r="E15">
-        <v>5.3130010012790905</v>
-      </c>
-      <c r="F15">
-        <v>10.7</v>
-      </c>
-      <c r="G15">
-        <v>99.528999999999996</v>
-      </c>
-      <c r="H15">
-        <v>99.82</v>
-      </c>
-      <c r="I15">
-        <v>903</v>
-      </c>
-      <c r="J15">
-        <v>11.237521099590065</v>
-      </c>
-      <c r="K15">
-        <v>173</v>
-      </c>
-      <c r="L15" s="12"/>
-      <c r="M15">
-        <v>84.4</v>
-      </c>
-      <c r="N15">
-        <v>64077</v>
-      </c>
-      <c r="O15">
-        <v>1113</v>
-      </c>
-      <c r="P15">
-        <v>332.28</v>
-      </c>
-      <c r="Q15">
-        <v>78</v>
-      </c>
-      <c r="R15">
-        <v>7529.41</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>398</v>
-      </c>
-      <c r="U15">
-        <v>22304</v>
-      </c>
-      <c r="V15">
-        <v>14801.1</v>
-      </c>
-      <c r="W15">
-        <v>7953</v>
-      </c>
-      <c r="X15">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="Y15">
-        <v>47.76</v>
-      </c>
-      <c r="Z15">
-        <v>20635</v>
-      </c>
-      <c r="AA15">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="AB15">
-        <v>565.54116252181666</v>
-      </c>
-      <c r="AC15">
-        <v>5.5821077980131237</v>
-      </c>
-      <c r="AD15">
-        <v>3862</v>
-      </c>
-      <c r="AE15">
-        <v>8375.73</v>
-      </c>
-      <c r="AF15">
-        <v>331.08</v>
-      </c>
-      <c r="AG15">
-        <v>2872.77</v>
-      </c>
-      <c r="AH15">
-        <v>11.33</v>
-      </c>
-      <c r="AI15">
-        <v>1575.65</v>
-      </c>
-      <c r="AJ15">
-        <v>2.1</v>
-      </c>
-      <c r="AK15">
-        <v>2839.2</v>
-      </c>
-      <c r="AL15">
-        <v>4.5</v>
-      </c>
-      <c r="AM15">
-        <v>3</v>
-      </c>
-      <c r="AN15">
-        <v>2412</v>
-      </c>
-      <c r="AO15">
-        <v>26.4</v>
-      </c>
-      <c r="AP15">
-        <v>7.1</v>
-      </c>
-      <c r="AQ15">
-        <v>53</v>
-      </c>
-      <c r="AR15">
-        <v>12.2</v>
-      </c>
-      <c r="AS15">
-        <v>1.73</v>
-      </c>
-      <c r="AT15">
-        <v>8.4</v>
-      </c>
-      <c r="AU15">
-        <v>5.2</v>
-      </c>
-      <c r="AV15">
-        <v>30.84</v>
-      </c>
-      <c r="AW15">
-        <v>25723</v>
-      </c>
-      <c r="AX15">
-        <v>413</v>
-      </c>
-      <c r="AY15">
-        <v>0.69402242170634154</v>
-      </c>
-      <c r="AZ15">
-        <v>9.0039054117849009</v>
-      </c>
-      <c r="BA15">
-        <v>8.6</v>
-      </c>
-      <c r="BB15">
-        <v>23979</v>
-      </c>
-      <c r="BC15">
-        <v>54.3</v>
-      </c>
-      <c r="BD15">
-        <v>59.9</v>
-      </c>
-      <c r="BE15">
-        <v>20.2</v>
-      </c>
-      <c r="BF15">
-        <v>70.900000000000006</v>
-      </c>
-    </row>
-    <row r="16" spans="1:58">
-      <c r="A16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B16">
-        <v>3487973</v>
-      </c>
-      <c r="C16">
-        <v>117</v>
-      </c>
-      <c r="D16">
-        <v>53.8</v>
-      </c>
-      <c r="E16">
-        <v>2.5928364006061786</v>
-      </c>
-      <c r="F16">
-        <v>13.4</v>
-      </c>
-      <c r="G16">
-        <v>99.72</v>
-      </c>
-      <c r="H16">
-        <v>100.06</v>
-      </c>
-      <c r="I16">
-        <v>966</v>
-      </c>
-      <c r="J16">
-        <v>12.532474741867436</v>
-      </c>
-      <c r="K16">
-        <v>324</v>
-      </c>
-      <c r="L16" s="12"/>
-      <c r="M16">
-        <v>83</v>
-      </c>
-      <c r="N16">
-        <v>95104</v>
-      </c>
-      <c r="O16">
-        <v>1491</v>
-      </c>
-      <c r="P16">
-        <v>596.51</v>
-      </c>
-      <c r="Q16">
-        <v>105</v>
-      </c>
-      <c r="R16">
-        <v>7759.22</v>
-      </c>
-      <c r="S16">
-        <v>0.25</v>
-      </c>
-      <c r="T16">
-        <v>1026.7</v>
-      </c>
-      <c r="U16">
-        <v>41167.4</v>
-      </c>
-      <c r="V16">
-        <v>31296.799999999999</v>
-      </c>
-      <c r="W16">
-        <v>17317</v>
-      </c>
-      <c r="X16">
-        <v>1.9</v>
-      </c>
-      <c r="Y16">
-        <v>90.44</v>
-      </c>
-      <c r="Z16">
-        <v>35094</v>
-      </c>
-      <c r="AA16">
-        <v>6.4</v>
-      </c>
-      <c r="AB16">
-        <v>656.32331442932616</v>
-      </c>
-      <c r="AC16">
-        <v>7.0786098401564459</v>
-      </c>
-      <c r="AD16">
-        <v>6894</v>
-      </c>
-      <c r="AE16">
-        <v>8604.0400000000009</v>
-      </c>
-      <c r="AF16">
-        <v>304.82</v>
-      </c>
-      <c r="AG16">
-        <v>3345.34</v>
-      </c>
-      <c r="AH16">
-        <v>21.1</v>
-      </c>
-      <c r="AI16">
-        <v>1557.5</v>
-      </c>
-      <c r="AJ16">
-        <v>1.8</v>
-      </c>
-      <c r="AK16">
-        <v>3278.7</v>
-      </c>
-      <c r="AL16">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="AM16">
-        <v>3</v>
-      </c>
-      <c r="AN16">
-        <v>1205</v>
-      </c>
-      <c r="AO16">
-        <v>30.7</v>
-      </c>
-      <c r="AP16">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="AQ16">
-        <v>48</v>
-      </c>
-      <c r="AR16">
-        <v>15.4</v>
-      </c>
-      <c r="AS16">
-        <v>1.91</v>
-      </c>
-      <c r="AT16">
-        <v>2.9</v>
-      </c>
-      <c r="AU16">
-        <v>3</v>
-      </c>
-      <c r="AV16">
-        <v>11.66</v>
-      </c>
-      <c r="AW16">
-        <v>11057</v>
-      </c>
-      <c r="AX16">
-        <v>398</v>
-      </c>
-      <c r="AY16">
-        <v>0.69195187210789089</v>
-      </c>
-      <c r="AZ16">
-        <v>8.1626506024096379</v>
-      </c>
-      <c r="BA16">
-        <v>4.3</v>
-      </c>
-      <c r="BB16">
-        <v>46662</v>
-      </c>
-      <c r="BC16">
-        <v>59.9</v>
-      </c>
-      <c r="BD16">
-        <v>59.6</v>
-      </c>
-      <c r="BE16">
-        <v>23.1</v>
-      </c>
-      <c r="BF16">
-        <v>70.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:58">
-      <c r="A17" t="s">
-        <v>140</v>
-      </c>
-      <c r="B17">
-        <v>1631784</v>
-      </c>
-      <c r="C17">
-        <v>72</v>
-      </c>
-      <c r="D17">
-        <v>68.400000000000006</v>
-      </c>
-      <c r="E17">
-        <v>4.6134561046644897</v>
-      </c>
-      <c r="F17">
-        <v>10.8</v>
-      </c>
-      <c r="G17">
-        <v>99.435000000000002</v>
-      </c>
-      <c r="H17">
-        <v>99.99</v>
-      </c>
-      <c r="I17">
-        <v>932</v>
-      </c>
-      <c r="J17">
-        <v>10.729815455594002</v>
-      </c>
-      <c r="K17">
-        <v>229</v>
-      </c>
-      <c r="L17" s="12"/>
-      <c r="M17">
-        <v>82.7</v>
-      </c>
-      <c r="N17">
-        <v>74398</v>
-      </c>
-      <c r="O17">
-        <v>1572</v>
-      </c>
-      <c r="P17">
-        <v>490.3</v>
-      </c>
-      <c r="Q17">
-        <v>104</v>
-      </c>
-      <c r="R17">
-        <v>8027.37</v>
-      </c>
-      <c r="S17">
-        <v>0.87</v>
-      </c>
-      <c r="T17">
-        <v>591.79999999999995</v>
-      </c>
-      <c r="U17">
-        <v>18676.5</v>
-      </c>
-      <c r="V17">
-        <v>14199.4</v>
-      </c>
-      <c r="W17">
-        <v>7554</v>
-      </c>
-      <c r="X17">
-        <v>1.4</v>
-      </c>
-      <c r="Y17">
-        <v>117.13</v>
-      </c>
-      <c r="Z17">
-        <v>29590</v>
-      </c>
-      <c r="AA17">
-        <v>5.4</v>
-      </c>
-      <c r="AB17">
-        <v>576.97158447441575</v>
-      </c>
-      <c r="AC17">
-        <v>4.5778117692047475</v>
-      </c>
-      <c r="AD17">
-        <v>5331</v>
-      </c>
-      <c r="AE17">
-        <v>9044.31</v>
-      </c>
-      <c r="AF17">
-        <v>359.04</v>
-      </c>
-      <c r="AG17">
-        <v>2901.72</v>
-      </c>
-      <c r="AH17">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="AI17">
-        <v>1655.63</v>
-      </c>
-      <c r="AJ17">
-        <v>2.1</v>
-      </c>
-      <c r="AK17">
-        <v>3632.9</v>
-      </c>
-      <c r="AL17">
-        <v>6</v>
-      </c>
-      <c r="AM17">
-        <v>3</v>
-      </c>
-      <c r="AN17">
-        <v>1755</v>
-      </c>
-      <c r="AO17">
-        <v>34</v>
-      </c>
-      <c r="AP17">
-        <v>10.7</v>
-      </c>
-      <c r="AQ17">
-        <v>48.1</v>
-      </c>
-      <c r="AR17">
-        <v>12.6</v>
-      </c>
-      <c r="AS17">
-        <v>1.53</v>
-      </c>
-      <c r="AT17">
-        <v>6.8</v>
-      </c>
-      <c r="AU17">
-        <v>3.3</v>
-      </c>
-      <c r="AV17">
-        <v>94.5</v>
-      </c>
-      <c r="AW17">
-        <v>101574</v>
-      </c>
-      <c r="AX17">
-        <v>445</v>
-      </c>
-      <c r="AY17">
-        <v>1.0582029732475284</v>
-      </c>
-      <c r="AZ17">
-        <v>18.27954099594206</v>
-      </c>
-      <c r="BA17">
-        <v>12.3</v>
-      </c>
-      <c r="BB17">
-        <v>42599</v>
-      </c>
-      <c r="BC17">
-        <v>58.1</v>
-      </c>
-      <c r="BD17">
-        <v>59.2</v>
-      </c>
-      <c r="BE17">
-        <v>22.6</v>
-      </c>
-      <c r="BF17">
-        <v>72.7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:58">
-      <c r="L18" s="12"/>
-    </row>
-    <row r="19" spans="1:58">
-      <c r="L19" s="12"/>
-    </row>
-    <row r="20" spans="1:58">
-      <c r="L20" s="12"/>
-    </row>
-    <row r="21" spans="1:58">
-      <c r="L21" s="12"/>
-    </row>
-    <row r="22" spans="1:58">
-      <c r="L22" s="12"/>
-      <c r="Y22" s="14"/>
-    </row>
-    <row r="23" spans="1:58">
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="J23" s="14"/>
-      <c r="L23" s="12"/>
-      <c r="Y23" s="14"/>
-    </row>
-    <row r="24" spans="1:58">
-      <c r="A24" s="19"/>
+    <row r="24" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A24" s="18"/>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
-      <c r="J24" s="14"/>
-      <c r="L24" s="12"/>
-      <c r="Y24" s="14"/>
     </row>
-    <row r="25" spans="1:58">
-      <c r="A25" s="19"/>
+    <row r="25" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A25" s="18"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
-      <c r="J25" s="14"/>
-      <c r="Y25" s="14"/>
     </row>
-    <row r="26" spans="1:58">
-      <c r="A26" s="19"/>
+    <row r="26" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A26" s="18"/>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
-      <c r="J26" s="14"/>
-      <c r="Y26" s="14"/>
     </row>
-    <row r="27" spans="1:58">
-      <c r="A27" s="19"/>
+    <row r="27" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A27" s="18"/>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
-      <c r="J27" s="14"/>
-      <c r="Y27" s="14"/>
     </row>
-    <row r="28" spans="1:58">
-      <c r="A28" s="19"/>
+    <row r="28" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A28" s="18"/>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
-      <c r="J28" s="14"/>
-      <c r="Y28" s="14"/>
     </row>
-    <row r="29" spans="1:58">
-      <c r="A29" s="19"/>
+    <row r="29" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A29" s="18"/>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
-      <c r="J29" s="14"/>
-      <c r="Y29" s="14"/>
     </row>
-    <row r="30" spans="1:58">
-      <c r="A30" s="19"/>
+    <row r="30" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A30" s="18"/>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
-      <c r="J30" s="14"/>
-      <c r="Y30" s="14"/>
     </row>
-    <row r="31" spans="1:58">
-      <c r="A31" s="19"/>
+    <row r="31" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A31" s="18"/>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
-      <c r="J31" s="14"/>
-      <c r="Y31" s="14"/>
     </row>
-    <row r="32" spans="1:58">
-      <c r="A32" s="19"/>
+    <row r="32" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A32" s="18"/>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
-      <c r="J32" s="14"/>
-      <c r="Y32" s="14"/>
     </row>
-    <row r="33" spans="1:25">
-      <c r="A33" s="19"/>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A33" s="18"/>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
-      <c r="J33" s="14"/>
-      <c r="Y33" s="14"/>
     </row>
-    <row r="34" spans="1:25">
-      <c r="A34" s="19"/>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A34" s="18"/>
       <c r="D34" s="13"/>
       <c r="E34" s="13"/>
-      <c r="J34" s="14"/>
       <c r="Y34" s="14"/>
     </row>
-    <row r="35" spans="1:25">
-      <c r="A35" s="19"/>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A35" s="18"/>
       <c r="D35" s="13"/>
       <c r="E35" s="13"/>
-      <c r="J35" s="14"/>
       <c r="Y35" s="14"/>
     </row>
-    <row r="36" spans="1:25">
-      <c r="A36" s="19"/>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A36" s="18"/>
       <c r="D36" s="13"/>
       <c r="E36" s="13"/>
       <c r="J36" s="14"/>
       <c r="Y36" s="14"/>
     </row>
-    <row r="37" spans="1:25">
-      <c r="A37" s="19"/>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A37" s="18"/>
       <c r="D37" s="13"/>
       <c r="E37" s="13"/>
       <c r="J37" s="14"/>
       <c r="Y37" s="14"/>
     </row>
-    <row r="38" spans="1:25">
-      <c r="A38" s="19"/>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A38" s="18"/>
       <c r="D38" s="13"/>
       <c r="E38" s="13"/>
       <c r="J38" s="14"/>
     </row>
-    <row r="39" spans="1:25">
-      <c r="A39" s="19"/>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A39" s="18"/>
       <c r="D39" s="13"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="A21:BF37">
     <sortCondition ref="A21:BF21"/>
   </sortState>
-  <conditionalFormatting sqref="C2:AA17 AD2:BF17">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThanOrEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D23:D38">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThanOrEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J23:J38">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThanOrEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y22:Y37">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="B2:Z17 AB2:BE17 D24:D38 C23 J36:J38 I23 Y34:Y37 X22:X23">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
